--- a/research/traditional_assets/database/data/jamaica/jamaica_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_green_renewable_energy.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.105572007782837</v>
+        <v>0.1053418277633799</v>
       </c>
       <c r="C2">
-        <v>124.175682524813</v>
+        <v>123.382570271288</v>
       </c>
       <c r="D2">
-        <v>104.475682524813</v>
+        <v>104.879570271288</v>
       </c>
       <c r="E2">
-        <v>-22.6</v>
+        <v>-21.403</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.197</v>
       </c>
       <c r="G2">
         <v>19.7</v>
@@ -1451,28 +1451,28 @@
         <v>7.205</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06020909999999999</v>
       </c>
       <c r="N2">
-        <v>7.205</v>
+        <v>7.1447909</v>
       </c>
       <c r="O2">
-        <v>1.80125</v>
+        <v>1.786197725</v>
       </c>
       <c r="P2">
-        <v>5.40375</v>
+        <v>5.358593175</v>
       </c>
       <c r="Q2">
-        <v>8.82375</v>
+        <v>8.778593175000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.105572007782837</v>
+        <v>0.1060248260236161</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5824200964226487</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.6662962907601</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1053418277633799</v>
+        <v>0.1051116477439228</v>
       </c>
       <c r="C3">
-        <v>123.382570271288</v>
+        <v>122.5925928788865</v>
       </c>
       <c r="D3">
-        <v>104.879570271288</v>
+        <v>105.2865928788865</v>
       </c>
       <c r="E3">
-        <v>-21.403</v>
+        <v>-20.206</v>
       </c>
       <c r="F3">
-        <v>1.197</v>
+        <v>2.394</v>
       </c>
       <c r="G3">
         <v>19.7</v>
@@ -1533,28 +1533,28 @@
         <v>7.205</v>
       </c>
       <c r="M3">
-        <v>0.06020909999999999</v>
+        <v>0.1204182</v>
       </c>
       <c r="N3">
-        <v>7.1447909</v>
+        <v>7.0845818</v>
       </c>
       <c r="O3">
-        <v>1.786197725</v>
+        <v>1.77114545</v>
       </c>
       <c r="P3">
-        <v>5.358593175</v>
+        <v>5.31343635</v>
       </c>
       <c r="Q3">
-        <v>8.778593175000001</v>
+        <v>8.73343635</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1060248260236161</v>
+        <v>0.1064868854529825</v>
       </c>
       <c r="T3">
-        <v>0.5824200964226487</v>
+        <v>0.5868885642485091</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.6662962907601</v>
+        <v>59.83314814538004</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1051116477439228</v>
+        <v>0.1048814677244657</v>
       </c>
       <c r="C4">
-        <v>122.5925928788865</v>
+        <v>121.8057869876459</v>
       </c>
       <c r="D4">
-        <v>105.2865928788865</v>
+        <v>105.6967869876459</v>
       </c>
       <c r="E4">
-        <v>-20.206</v>
+        <v>-19.009</v>
       </c>
       <c r="F4">
-        <v>2.394</v>
+        <v>3.591</v>
       </c>
       <c r="G4">
         <v>19.7</v>
@@ -1615,28 +1615,28 @@
         <v>7.205</v>
       </c>
       <c r="M4">
-        <v>0.1204182</v>
+        <v>0.1806273</v>
       </c>
       <c r="N4">
-        <v>7.0845818</v>
+        <v>7.0243727</v>
       </c>
       <c r="O4">
-        <v>1.77114545</v>
+        <v>1.756093175</v>
       </c>
       <c r="P4">
-        <v>5.31343635</v>
+        <v>5.268279525</v>
       </c>
       <c r="Q4">
-        <v>8.73343635</v>
+        <v>8.688279524999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1064868854529825</v>
+        <v>0.1069584718808925</v>
       </c>
       <c r="T4">
-        <v>0.5868885642485091</v>
+        <v>0.5914491654316038</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.83314814538004</v>
+        <v>39.88876543025334</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1048814677244657</v>
+        <v>0.1046512877050086</v>
       </c>
       <c r="C5">
-        <v>121.8057869876459</v>
+        <v>121.0221898108316</v>
       </c>
       <c r="D5">
-        <v>105.6967869876459</v>
+        <v>106.1101898108316</v>
       </c>
       <c r="E5">
-        <v>-19.009</v>
+        <v>-17.812</v>
       </c>
       <c r="F5">
-        <v>3.591</v>
+        <v>4.787999999999999</v>
       </c>
       <c r="G5">
         <v>19.7</v>
@@ -1697,28 +1697,28 @@
         <v>7.205</v>
       </c>
       <c r="M5">
-        <v>0.1806273</v>
+        <v>0.2408364</v>
       </c>
       <c r="N5">
-        <v>7.0243727</v>
+        <v>6.9641636</v>
       </c>
       <c r="O5">
-        <v>1.756093175</v>
+        <v>1.7410409</v>
       </c>
       <c r="P5">
-        <v>5.268279525</v>
+        <v>5.2231227</v>
       </c>
       <c r="Q5">
-        <v>8.688279524999999</v>
+        <v>8.643122699999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1069584718808925</v>
+        <v>0.1074398830260506</v>
       </c>
       <c r="T5">
-        <v>0.5914491654316038</v>
+        <v>0.5961047791393462</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.88876543025334</v>
+        <v>29.91657407269001</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1046512877050086</v>
+        <v>0.1044211076855515</v>
       </c>
       <c r="C6">
-        <v>121.0221898108316</v>
+        <v>120.2418391461916</v>
       </c>
       <c r="D6">
-        <v>106.1101898108316</v>
+        <v>106.5268391461916</v>
       </c>
       <c r="E6">
-        <v>-17.812</v>
+        <v>-16.615</v>
       </c>
       <c r="F6">
-        <v>4.787999999999999</v>
+        <v>5.984999999999999</v>
       </c>
       <c r="G6">
         <v>19.7</v>
@@ -1779,28 +1779,28 @@
         <v>7.205</v>
       </c>
       <c r="M6">
-        <v>0.2408364</v>
+        <v>0.3010455</v>
       </c>
       <c r="N6">
-        <v>6.9641636</v>
+        <v>6.9039545</v>
       </c>
       <c r="O6">
-        <v>1.7410409</v>
+        <v>1.725988625</v>
       </c>
       <c r="P6">
-        <v>5.2231227</v>
+        <v>5.177965875</v>
       </c>
       <c r="Q6">
-        <v>8.643122699999999</v>
+        <v>8.597965875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1074398830260506</v>
+        <v>0.1079314291426858</v>
       </c>
       <c r="T6">
-        <v>0.5961047791393462</v>
+        <v>0.6008584057672517</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.91657407269001</v>
+        <v>23.93325925815201</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1044211076855515</v>
+        <v>0.1041909276660944</v>
       </c>
       <c r="C7">
-        <v>120.2418391461916</v>
+        <v>119.4647733874764</v>
       </c>
       <c r="D7">
-        <v>106.5268391461916</v>
+        <v>106.9467733874764</v>
       </c>
       <c r="E7">
-        <v>-16.615</v>
+        <v>-15.418</v>
       </c>
       <c r="F7">
-        <v>5.984999999999999</v>
+        <v>7.181999999999999</v>
       </c>
       <c r="G7">
         <v>19.7</v>
@@ -1861,28 +1861,28 @@
         <v>7.205</v>
       </c>
       <c r="M7">
-        <v>0.3010455</v>
+        <v>0.3612546</v>
       </c>
       <c r="N7">
-        <v>6.9039545</v>
+        <v>6.8437454</v>
       </c>
       <c r="O7">
-        <v>1.725988625</v>
+        <v>1.71093635</v>
       </c>
       <c r="P7">
-        <v>5.177965875</v>
+        <v>5.132809050000001</v>
       </c>
       <c r="Q7">
-        <v>8.597965875</v>
+        <v>8.55280905</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1079314291426858</v>
+        <v>0.1084334336873345</v>
       </c>
       <c r="T7">
-        <v>0.6008584057672517</v>
+        <v>0.6057131733872403</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.93325925815201</v>
+        <v>19.94438271512668</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1041909276660944</v>
+        <v>0.1039607476466374</v>
       </c>
       <c r="C8">
-        <v>119.4647733874764</v>
+        <v>118.6910315362327</v>
       </c>
       <c r="D8">
-        <v>106.9467733874764</v>
+        <v>107.3700315362327</v>
       </c>
       <c r="E8">
-        <v>-15.418</v>
+        <v>-14.221</v>
       </c>
       <c r="F8">
-        <v>7.181999999999999</v>
+        <v>8.378999999999998</v>
       </c>
       <c r="G8">
         <v>19.7</v>
@@ -1943,28 +1943,28 @@
         <v>7.205</v>
       </c>
       <c r="M8">
-        <v>0.3612546</v>
+        <v>0.4214636999999999</v>
       </c>
       <c r="N8">
-        <v>6.8437454</v>
+        <v>6.7835363</v>
       </c>
       <c r="O8">
-        <v>1.71093635</v>
+        <v>1.695884075</v>
       </c>
       <c r="P8">
-        <v>5.132809050000001</v>
+        <v>5.087652224999999</v>
       </c>
       <c r="Q8">
-        <v>8.55280905</v>
+        <v>8.507652224999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1084334336873345</v>
+        <v>0.1089462340286423</v>
       </c>
       <c r="T8">
-        <v>0.6057131733872403</v>
+        <v>0.6106723446119597</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.94438271512668</v>
+        <v>17.0951851843943</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1039607476466373</v>
+        <v>0.1037305676271803</v>
       </c>
       <c r="C9">
-        <v>118.6910315362328</v>
+        <v>117.9206532138792</v>
       </c>
       <c r="D9">
-        <v>107.3700315362328</v>
+        <v>107.7966532138792</v>
       </c>
       <c r="E9">
-        <v>-14.221</v>
+        <v>-13.024</v>
       </c>
       <c r="F9">
-        <v>8.379</v>
+        <v>9.575999999999999</v>
       </c>
       <c r="G9">
         <v>19.7</v>
@@ -2025,28 +2025,28 @@
         <v>7.205</v>
       </c>
       <c r="M9">
-        <v>0.4214636999999999</v>
+        <v>0.4816727999999999</v>
       </c>
       <c r="N9">
-        <v>6.7835363</v>
+        <v>6.7233272</v>
       </c>
       <c r="O9">
-        <v>1.695884075</v>
+        <v>1.6808318</v>
       </c>
       <c r="P9">
-        <v>5.087652224999999</v>
+        <v>5.0424954</v>
       </c>
       <c r="Q9">
-        <v>8.507652224999999</v>
+        <v>8.4624954</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1089462340286423</v>
+        <v>0.1094701822034568</v>
       </c>
       <c r="T9">
-        <v>0.6106723446119597</v>
+        <v>0.6157393239067819</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.09518518439429</v>
+        <v>14.95828703634501</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1037305676271803</v>
+        <v>0.1035003876077231</v>
       </c>
       <c r="C10">
-        <v>117.9206532138792</v>
+        <v>117.1536786740697</v>
       </c>
       <c r="D10">
-        <v>107.7966532138792</v>
+        <v>108.2266786740697</v>
       </c>
       <c r="E10">
-        <v>-13.024</v>
+        <v>-11.827</v>
       </c>
       <c r="F10">
-        <v>9.575999999999999</v>
+        <v>10.773</v>
       </c>
       <c r="G10">
         <v>19.7</v>
@@ -2107,28 +2107,28 @@
         <v>7.205</v>
       </c>
       <c r="M10">
-        <v>0.4816727999999999</v>
+        <v>0.5418818999999999</v>
       </c>
       <c r="N10">
-        <v>6.7233272</v>
+        <v>6.6631181</v>
       </c>
       <c r="O10">
-        <v>1.6808318</v>
+        <v>1.665779525</v>
       </c>
       <c r="P10">
-        <v>5.0424954</v>
+        <v>4.997338575000001</v>
       </c>
       <c r="Q10">
-        <v>8.4624954</v>
+        <v>8.417338575</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1094701822034568</v>
+        <v>0.1100056457227727</v>
       </c>
       <c r="T10">
-        <v>0.6157393239067819</v>
+        <v>0.6209176653839077</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.95828703634501</v>
+        <v>13.29625514341778</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1035003876077231</v>
+        <v>0.1033827075882661</v>
       </c>
       <c r="C11">
-        <v>117.1536786740697</v>
+        <v>116.1778582292794</v>
       </c>
       <c r="D11">
-        <v>108.2266786740697</v>
+        <v>108.4478582292794</v>
       </c>
       <c r="E11">
-        <v>-11.827</v>
+        <v>-10.63</v>
       </c>
       <c r="F11">
-        <v>10.773</v>
+        <v>11.97</v>
       </c>
       <c r="G11">
         <v>19.7</v>
@@ -2189,45 +2189,45 @@
         <v>7.205</v>
       </c>
       <c r="M11">
-        <v>0.5418818999999999</v>
+        <v>0.6200459999999999</v>
       </c>
       <c r="N11">
-        <v>6.6631181</v>
+        <v>6.584954</v>
       </c>
       <c r="O11">
-        <v>1.665779525</v>
+        <v>1.6462385</v>
       </c>
       <c r="P11">
-        <v>4.997338575000001</v>
+        <v>4.9387155</v>
       </c>
       <c r="Q11">
-        <v>8.417338575</v>
+        <v>8.358715499999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1100056457227727</v>
+        <v>0.1105530084314067</v>
       </c>
       <c r="T11">
-        <v>0.6209176653839077</v>
+        <v>0.6262110811160808</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.29625514341778</v>
+        <v>11.62010560506801</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1033827075882661</v>
+        <v>0.103163777568809</v>
       </c>
       <c r="C12">
-        <v>116.1778582292794</v>
+        <v>115.394751677697</v>
       </c>
       <c r="D12">
-        <v>108.4478582292794</v>
+        <v>108.861751677697</v>
       </c>
       <c r="E12">
-        <v>-10.63</v>
+        <v>-9.433000000000003</v>
       </c>
       <c r="F12">
-        <v>11.97</v>
+        <v>13.167</v>
       </c>
       <c r="G12">
         <v>19.7</v>
@@ -2271,28 +2271,28 @@
         <v>7.205</v>
       </c>
       <c r="M12">
-        <v>0.6200459999999999</v>
+        <v>0.6820505999999998</v>
       </c>
       <c r="N12">
-        <v>6.584954</v>
+        <v>6.5229494</v>
       </c>
       <c r="O12">
-        <v>1.6462385</v>
+        <v>1.63073735</v>
       </c>
       <c r="P12">
-        <v>4.9387155</v>
+        <v>4.892212049999999</v>
       </c>
       <c r="Q12">
-        <v>8.358715499999999</v>
+        <v>8.312212049999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1105530084314067</v>
+        <v>0.1111126714256281</v>
       </c>
       <c r="T12">
-        <v>0.6262110811160808</v>
+        <v>0.6316234500107748</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.62010560506801</v>
+        <v>10.56373236824365</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.103163777568809</v>
+        <v>0.1030978475493519</v>
       </c>
       <c r="C13">
-        <v>115.394751677697</v>
+        <v>114.3230139294781</v>
       </c>
       <c r="D13">
-        <v>108.861751677697</v>
+        <v>108.9870139294781</v>
       </c>
       <c r="E13">
-        <v>-9.433000000000003</v>
+        <v>-8.236000000000002</v>
       </c>
       <c r="F13">
-        <v>13.167</v>
+        <v>14.364</v>
       </c>
       <c r="G13">
         <v>19.7</v>
@@ -2353,45 +2353,45 @@
         <v>7.205</v>
       </c>
       <c r="M13">
-        <v>0.6820505999999998</v>
+        <v>0.7684739999999999</v>
       </c>
       <c r="N13">
-        <v>6.5229494</v>
+        <v>6.436526000000001</v>
       </c>
       <c r="O13">
-        <v>1.63073735</v>
+        <v>1.6091315</v>
       </c>
       <c r="P13">
-        <v>4.892212049999999</v>
+        <v>4.8273945</v>
       </c>
       <c r="Q13">
-        <v>8.312212049999999</v>
+        <v>8.2473945</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1111126714256281</v>
+        <v>0.1116850540333544</v>
       </c>
       <c r="T13">
-        <v>0.6316234500107748</v>
+        <v>0.637158827289439</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.56373236824365</v>
+        <v>9.375723837110952</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1030978475493519</v>
+        <v>0.1028916675298948</v>
       </c>
       <c r="C14">
-        <v>114.3230139294781</v>
+        <v>113.5196080496846</v>
       </c>
       <c r="D14">
-        <v>108.9870139294781</v>
+        <v>109.3806080496846</v>
       </c>
       <c r="E14">
-        <v>-8.236000000000002</v>
+        <v>-7.039000000000003</v>
       </c>
       <c r="F14">
-        <v>14.364</v>
+        <v>15.561</v>
       </c>
       <c r="G14">
         <v>19.7</v>
@@ -2435,28 +2435,28 @@
         <v>7.205</v>
       </c>
       <c r="M14">
-        <v>0.7684739999999999</v>
+        <v>0.8325134999999999</v>
       </c>
       <c r="N14">
-        <v>6.436526000000001</v>
+        <v>6.3724865</v>
       </c>
       <c r="O14">
-        <v>1.6091315</v>
+        <v>1.593121625</v>
       </c>
       <c r="P14">
-        <v>4.8273945</v>
+        <v>4.779364875</v>
       </c>
       <c r="Q14">
-        <v>8.2473945</v>
+        <v>8.199364875000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1116850540333544</v>
+        <v>0.112270594861948</v>
       </c>
       <c r="T14">
-        <v>0.637158827289439</v>
+        <v>0.6428214546204862</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.375723837110952</v>
+        <v>8.654514311179339</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1028916675298948</v>
+        <v>0.1026854875104377</v>
       </c>
       <c r="C15">
-        <v>113.5196080496846</v>
+        <v>112.7190553138796</v>
       </c>
       <c r="D15">
-        <v>109.3806080496846</v>
+        <v>109.7770553138796</v>
       </c>
       <c r="E15">
-        <v>-7.039000000000003</v>
+        <v>-5.842000000000002</v>
       </c>
       <c r="F15">
-        <v>15.561</v>
+        <v>16.758</v>
       </c>
       <c r="G15">
         <v>19.7</v>
@@ -2517,28 +2517,28 @@
         <v>7.205</v>
       </c>
       <c r="M15">
-        <v>0.8325134999999999</v>
+        <v>0.8965529999999999</v>
       </c>
       <c r="N15">
-        <v>6.3724865</v>
+        <v>6.308447</v>
       </c>
       <c r="O15">
-        <v>1.593121625</v>
+        <v>1.57711175</v>
       </c>
       <c r="P15">
-        <v>4.779364875</v>
+        <v>4.73133525</v>
       </c>
       <c r="Q15">
-        <v>8.199364875000001</v>
+        <v>8.151335249999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.112270594861948</v>
+        <v>0.1128697529191136</v>
       </c>
       <c r="T15">
-        <v>0.6428214546204862</v>
+        <v>0.6486157709592323</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.654514311179339</v>
+        <v>8.036334717523673</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1026854875104377</v>
+        <v>0.1025693074909806</v>
       </c>
       <c r="C16">
-        <v>112.7190553138796</v>
+        <v>111.7467172128175</v>
       </c>
       <c r="D16">
-        <v>109.7770553138796</v>
+        <v>110.0017172128175</v>
       </c>
       <c r="E16">
-        <v>-5.842000000000002</v>
+        <v>-4.645</v>
       </c>
       <c r="F16">
-        <v>16.758</v>
+        <v>17.955</v>
       </c>
       <c r="G16">
         <v>19.7</v>
@@ -2599,45 +2599,45 @@
         <v>7.205</v>
       </c>
       <c r="M16">
-        <v>0.8965529999999999</v>
+        <v>0.9749565000000001</v>
       </c>
       <c r="N16">
-        <v>6.308447</v>
+        <v>6.2300435</v>
       </c>
       <c r="O16">
-        <v>1.57711175</v>
+        <v>1.557510875</v>
       </c>
       <c r="P16">
-        <v>4.73133525</v>
+        <v>4.672532625</v>
       </c>
       <c r="Q16">
-        <v>8.151335249999999</v>
+        <v>8.092532625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1128697529191136</v>
+        <v>0.1134830088129183</v>
       </c>
       <c r="T16">
-        <v>0.6486157709592323</v>
+        <v>0.6545464241530076</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.036334717523673</v>
+        <v>7.390073300706236</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1025693074909806</v>
+        <v>0.1023691274715235</v>
       </c>
       <c r="C17">
-        <v>111.7467172128175</v>
+        <v>110.9389780495355</v>
       </c>
       <c r="D17">
-        <v>110.0017172128175</v>
+        <v>110.3909780495355</v>
       </c>
       <c r="E17">
-        <v>-4.645000000000003</v>
+        <v>-3.448000000000004</v>
       </c>
       <c r="F17">
-        <v>17.955</v>
+        <v>19.152</v>
       </c>
       <c r="G17">
         <v>19.7</v>
@@ -2681,28 +2681,28 @@
         <v>7.205</v>
       </c>
       <c r="M17">
-        <v>0.9749564999999999</v>
+        <v>1.0399536</v>
       </c>
       <c r="N17">
-        <v>6.2300435</v>
+        <v>6.1650464</v>
       </c>
       <c r="O17">
-        <v>1.557510875</v>
+        <v>1.5412616</v>
       </c>
       <c r="P17">
-        <v>4.672532625</v>
+        <v>4.6237848</v>
       </c>
       <c r="Q17">
-        <v>8.092532625</v>
+        <v>8.043784800000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1134830088129183</v>
+        <v>0.114110866037528</v>
       </c>
       <c r="T17">
-        <v>0.6545464241530076</v>
+        <v>0.6606182833752062</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.390073300706237</v>
+        <v>6.928193719412098</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1023691274715235</v>
+        <v>0.1021689474520664</v>
       </c>
       <c r="C18">
-        <v>110.9389780495355</v>
+        <v>110.1340036085125</v>
       </c>
       <c r="D18">
-        <v>110.3909780495355</v>
+        <v>110.7830036085125</v>
       </c>
       <c r="E18">
-        <v>-3.448000000000004</v>
+        <v>-2.251000000000001</v>
       </c>
       <c r="F18">
-        <v>19.152</v>
+        <v>20.349</v>
       </c>
       <c r="G18">
         <v>19.7</v>
@@ -2763,28 +2763,28 @@
         <v>7.205</v>
       </c>
       <c r="M18">
-        <v>1.0399536</v>
+        <v>1.1049507</v>
       </c>
       <c r="N18">
-        <v>6.1650464</v>
+        <v>6.1000493</v>
       </c>
       <c r="O18">
-        <v>1.5412616</v>
+        <v>1.525012325</v>
       </c>
       <c r="P18">
-        <v>4.6237848</v>
+        <v>4.575036975</v>
       </c>
       <c r="Q18">
-        <v>8.043784800000001</v>
+        <v>7.995036975</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.114110866037528</v>
+        <v>0.1147538523518873</v>
       </c>
       <c r="T18">
-        <v>0.6606182833752062</v>
+        <v>0.6668364524581808</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.928193719412098</v>
+        <v>6.520652912387856</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1021689474520664</v>
+        <v>0.1019687674326093</v>
       </c>
       <c r="C19">
-        <v>110.1340036085125</v>
+        <v>109.3318234493516</v>
       </c>
       <c r="D19">
-        <v>110.7830036085125</v>
+        <v>111.1778234493515</v>
       </c>
       <c r="E19">
-        <v>-2.251000000000001</v>
+        <v>-1.054000000000002</v>
       </c>
       <c r="F19">
-        <v>20.349</v>
+        <v>21.546</v>
       </c>
       <c r="G19">
         <v>19.7</v>
@@ -2845,28 +2845,28 @@
         <v>7.205</v>
       </c>
       <c r="M19">
-        <v>1.1049507</v>
+        <v>1.1699478</v>
       </c>
       <c r="N19">
-        <v>6.1000493</v>
+        <v>6.0350522</v>
       </c>
       <c r="O19">
-        <v>1.525012325</v>
+        <v>1.50876305</v>
       </c>
       <c r="P19">
-        <v>4.575036975</v>
+        <v>4.52628915</v>
       </c>
       <c r="Q19">
-        <v>7.995036975</v>
+        <v>7.94628915</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1147538523518873</v>
+        <v>0.1154125212592797</v>
       </c>
       <c r="T19">
-        <v>0.6668364524581808</v>
+        <v>0.6732062842017155</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.520652912387856</v>
+        <v>6.158394417255197</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1019687674326093</v>
+        <v>0.1019110874131523</v>
       </c>
       <c r="C20">
-        <v>109.3318234493515</v>
+        <v>108.2491099355951</v>
       </c>
       <c r="D20">
-        <v>111.1778234493515</v>
+        <v>111.2921099355951</v>
       </c>
       <c r="E20">
-        <v>-1.054000000000006</v>
+        <v>0.1429999999999971</v>
       </c>
       <c r="F20">
-        <v>21.546</v>
+        <v>22.743</v>
       </c>
       <c r="G20">
         <v>19.7</v>
@@ -2927,45 +2927,45 @@
         <v>7.205</v>
       </c>
       <c r="M20">
-        <v>1.1699478</v>
+        <v>1.2576879</v>
       </c>
       <c r="N20">
-        <v>6.0350522</v>
+        <v>5.9473121</v>
       </c>
       <c r="O20">
-        <v>1.50876305</v>
+        <v>1.486828025</v>
       </c>
       <c r="P20">
-        <v>4.52628915</v>
+        <v>4.460484075</v>
       </c>
       <c r="Q20">
-        <v>7.94628915</v>
+        <v>7.880484075</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1154125212592797</v>
+        <v>0.1160874535964843</v>
       </c>
       <c r="T20">
-        <v>0.6732062842017155</v>
+        <v>0.679733395741387</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.158394417255198</v>
+        <v>5.728766254330666</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1019110874131523</v>
+        <v>0.1017184073936951</v>
       </c>
       <c r="C21">
-        <v>108.2491099355951</v>
+        <v>107.4355930658788</v>
       </c>
       <c r="D21">
-        <v>111.2921099355951</v>
+        <v>111.6755930658788</v>
       </c>
       <c r="E21">
-        <v>0.1429999999999971</v>
+        <v>1.339999999999996</v>
       </c>
       <c r="F21">
-        <v>22.743</v>
+        <v>23.94</v>
       </c>
       <c r="G21">
         <v>19.7</v>
@@ -3009,28 +3009,28 @@
         <v>7.205</v>
       </c>
       <c r="M21">
-        <v>1.2576879</v>
+        <v>1.323882</v>
       </c>
       <c r="N21">
-        <v>5.9473121</v>
+        <v>5.881118</v>
       </c>
       <c r="O21">
-        <v>1.486828025</v>
+        <v>1.4702795</v>
       </c>
       <c r="P21">
-        <v>4.460484075</v>
+        <v>4.4108385</v>
       </c>
       <c r="Q21">
-        <v>7.880484075</v>
+        <v>7.8308385</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1160874535964843</v>
+        <v>0.1167792592421189</v>
       </c>
       <c r="T21">
-        <v>0.679733395741387</v>
+        <v>0.6864236850695502</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.728766254330666</v>
+        <v>5.442327941614131</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1017184073936951</v>
+        <v>0.101525727374238</v>
       </c>
       <c r="C22">
-        <v>107.4355930658788</v>
+        <v>106.624728096478</v>
       </c>
       <c r="D22">
-        <v>111.6755930658788</v>
+        <v>112.061728096478</v>
       </c>
       <c r="E22">
-        <v>1.339999999999996</v>
+        <v>2.536999999999999</v>
       </c>
       <c r="F22">
-        <v>23.94</v>
+        <v>25.137</v>
       </c>
       <c r="G22">
         <v>19.7</v>
@@ -3091,28 +3091,28 @@
         <v>7.205</v>
       </c>
       <c r="M22">
-        <v>1.323882</v>
+        <v>1.3900761</v>
       </c>
       <c r="N22">
-        <v>5.881118</v>
+        <v>5.8149239</v>
       </c>
       <c r="O22">
-        <v>1.4702795</v>
+        <v>1.453730975</v>
       </c>
       <c r="P22">
-        <v>4.4108385</v>
+        <v>4.361192925</v>
       </c>
       <c r="Q22">
-        <v>7.8308385</v>
+        <v>7.781192925</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1167792592421189</v>
+        <v>0.1174885789547317</v>
       </c>
       <c r="T22">
-        <v>0.6864236850695502</v>
+        <v>0.6932833488110847</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.442327941614131</v>
+        <v>5.183169468203935</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.101525727374238</v>
+        <v>0.101333047354781</v>
       </c>
       <c r="C23">
-        <v>106.624728096478</v>
+        <v>105.8165426308593</v>
       </c>
       <c r="D23">
-        <v>112.061728096478</v>
+        <v>112.4505426308593</v>
       </c>
       <c r="E23">
-        <v>2.536999999999995</v>
+        <v>3.733999999999995</v>
       </c>
       <c r="F23">
-        <v>25.137</v>
+        <v>26.334</v>
       </c>
       <c r="G23">
         <v>19.7</v>
@@ -3173,28 +3173,28 @@
         <v>7.205</v>
       </c>
       <c r="M23">
-        <v>1.3900761</v>
+        <v>1.4562702</v>
       </c>
       <c r="N23">
-        <v>5.8149239</v>
+        <v>5.7487298</v>
       </c>
       <c r="O23">
-        <v>1.453730975</v>
+        <v>1.43718245</v>
       </c>
       <c r="P23">
-        <v>4.361192925</v>
+        <v>4.311547350000001</v>
       </c>
       <c r="Q23">
-        <v>7.781192925</v>
+        <v>7.73154735</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1174885789547317</v>
+        <v>0.1182160863522833</v>
       </c>
       <c r="T23">
-        <v>0.6932833488110847</v>
+        <v>0.7003189013665047</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.183169468203936</v>
+        <v>4.947570856012848</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.101333047354781</v>
+        <v>0.1011403673353239</v>
       </c>
       <c r="C24">
-        <v>105.8165426308593</v>
+        <v>105.0110646569201</v>
       </c>
       <c r="D24">
-        <v>112.4505426308593</v>
+        <v>112.8420646569201</v>
       </c>
       <c r="E24">
-        <v>3.733999999999995</v>
+        <v>4.930999999999997</v>
       </c>
       <c r="F24">
-        <v>26.334</v>
+        <v>27.531</v>
       </c>
       <c r="G24">
         <v>19.7</v>
@@ -3255,28 +3255,28 @@
         <v>7.205</v>
       </c>
       <c r="M24">
-        <v>1.4562702</v>
+        <v>1.5224643</v>
       </c>
       <c r="N24">
-        <v>5.7487298</v>
+        <v>5.6825357</v>
       </c>
       <c r="O24">
-        <v>1.43718245</v>
+        <v>1.420633925</v>
       </c>
       <c r="P24">
-        <v>4.311547350000001</v>
+        <v>4.261901775</v>
       </c>
       <c r="Q24">
-        <v>7.73154735</v>
+        <v>7.681901775</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1182160863522833</v>
+        <v>0.1189624900458751</v>
       </c>
       <c r="T24">
-        <v>0.7003189013665047</v>
+        <v>0.7075371955467408</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.947570856012848</v>
+        <v>4.732459079664462</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1011403673353239</v>
+        <v>0.1009476873158668</v>
       </c>
       <c r="C25">
-        <v>105.0110646569201</v>
+        <v>104.2083225537044</v>
       </c>
       <c r="D25">
-        <v>112.8420646569201</v>
+        <v>113.2363225537044</v>
       </c>
       <c r="E25">
-        <v>4.930999999999997</v>
+        <v>6.127999999999997</v>
       </c>
       <c r="F25">
-        <v>27.531</v>
+        <v>28.728</v>
       </c>
       <c r="G25">
         <v>19.7</v>
@@ -3337,28 +3337,28 @@
         <v>7.205</v>
       </c>
       <c r="M25">
-        <v>1.5224643</v>
+        <v>1.5886584</v>
       </c>
       <c r="N25">
-        <v>5.6825357</v>
+        <v>5.6163416</v>
       </c>
       <c r="O25">
-        <v>1.420633925</v>
+        <v>1.4040854</v>
       </c>
       <c r="P25">
-        <v>4.261901775</v>
+        <v>4.212256200000001</v>
       </c>
       <c r="Q25">
-        <v>7.681901775</v>
+        <v>7.6322562</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1189624900458751</v>
+        <v>0.11972853594193</v>
       </c>
       <c r="T25">
-        <v>0.7075371955467408</v>
+        <v>0.7149454448369831</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.732459079664462</v>
+        <v>4.535273284678444</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1009476873158668</v>
+        <v>0.1012237572964097</v>
       </c>
       <c r="C26">
-        <v>104.2083225537044</v>
+        <v>102.4472837571833</v>
       </c>
       <c r="D26">
-        <v>113.2363225537044</v>
+        <v>112.6722837571833</v>
       </c>
       <c r="E26">
-        <v>6.127999999999997</v>
+        <v>7.324999999999996</v>
       </c>
       <c r="F26">
-        <v>28.728</v>
+        <v>29.925</v>
       </c>
       <c r="G26">
         <v>19.7</v>
@@ -3419,45 +3419,45 @@
         <v>7.205</v>
       </c>
       <c r="M26">
-        <v>1.5886584</v>
+        <v>1.729665</v>
       </c>
       <c r="N26">
-        <v>5.6163416</v>
+        <v>5.475335</v>
       </c>
       <c r="O26">
-        <v>1.4040854</v>
+        <v>1.36883375</v>
       </c>
       <c r="P26">
-        <v>4.212256200000001</v>
+        <v>4.10650125</v>
       </c>
       <c r="Q26">
-        <v>7.6322562</v>
+        <v>7.52650125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.11972853594193</v>
+        <v>0.1205150097285462</v>
       </c>
       <c r="T26">
-        <v>0.7149454448369831</v>
+        <v>0.7225512474416318</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.535273284678444</v>
+        <v>4.165546507560713</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1012237572964097</v>
+        <v>0.1010498272769526</v>
       </c>
       <c r="C27">
-        <v>102.4472837571833</v>
+        <v>101.6049833729472</v>
       </c>
       <c r="D27">
-        <v>112.6722837571833</v>
+        <v>113.0269833729472</v>
       </c>
       <c r="E27">
-        <v>7.324999999999996</v>
+        <v>8.521999999999995</v>
       </c>
       <c r="F27">
-        <v>29.925</v>
+        <v>31.122</v>
       </c>
       <c r="G27">
         <v>19.7</v>
@@ -3501,28 +3501,28 @@
         <v>7.205</v>
       </c>
       <c r="M27">
-        <v>1.729665</v>
+        <v>1.7988516</v>
       </c>
       <c r="N27">
-        <v>5.475335</v>
+        <v>5.4061484</v>
       </c>
       <c r="O27">
-        <v>1.36883375</v>
+        <v>1.3515371</v>
       </c>
       <c r="P27">
-        <v>4.10650125</v>
+        <v>4.0546113</v>
       </c>
       <c r="Q27">
-        <v>7.52650125</v>
+        <v>7.4746113</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1205150097285462</v>
+        <v>0.1213227395634494</v>
       </c>
       <c r="T27">
-        <v>0.7225512474416318</v>
+        <v>0.7303626122788387</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.165546507560713</v>
+        <v>4.00533318034684</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1010498272769526</v>
+        <v>0.1015846472574955</v>
       </c>
       <c r="C28">
-        <v>101.6049833729472</v>
+        <v>99.32436822038886</v>
       </c>
       <c r="D28">
-        <v>113.0269833729472</v>
+        <v>111.9433682203889</v>
       </c>
       <c r="E28">
-        <v>8.521999999999995</v>
+        <v>9.718999999999994</v>
       </c>
       <c r="F28">
-        <v>31.122</v>
+        <v>32.319</v>
       </c>
       <c r="G28">
         <v>19.7</v>
@@ -3583,45 +3583,45 @@
         <v>7.205</v>
       </c>
       <c r="M28">
-        <v>1.7988516</v>
+        <v>1.9811547</v>
       </c>
       <c r="N28">
-        <v>5.4061484</v>
+        <v>5.223845300000001</v>
       </c>
       <c r="O28">
-        <v>1.3515371</v>
+        <v>1.305961325</v>
       </c>
       <c r="P28">
-        <v>4.0546113</v>
+        <v>3.917883975000001</v>
       </c>
       <c r="Q28">
-        <v>7.4746113</v>
+        <v>7.337883975</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1213227395634494</v>
+        <v>0.1221525989828706</v>
       </c>
       <c r="T28">
-        <v>0.7303626122788387</v>
+        <v>0.7383879871115855</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.00533318034684</v>
+        <v>3.636767991919057</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1015846472574955</v>
+        <v>0.1014369672380384</v>
       </c>
       <c r="C29">
-        <v>99.32436822038886</v>
+        <v>98.42450517118905</v>
       </c>
       <c r="D29">
-        <v>111.9433682203889</v>
+        <v>112.240505171189</v>
       </c>
       <c r="E29">
-        <v>9.718999999999994</v>
+        <v>10.916</v>
       </c>
       <c r="F29">
-        <v>32.319</v>
+        <v>33.516</v>
       </c>
       <c r="G29">
         <v>19.7</v>
@@ -3665,28 +3665,28 @@
         <v>7.205</v>
       </c>
       <c r="M29">
-        <v>1.9811547</v>
+        <v>2.0545308</v>
       </c>
       <c r="N29">
-        <v>5.223845300000001</v>
+        <v>5.1504692</v>
       </c>
       <c r="O29">
-        <v>1.305961325</v>
+        <v>1.2876173</v>
       </c>
       <c r="P29">
-        <v>3.917883975000001</v>
+        <v>3.8628519</v>
       </c>
       <c r="Q29">
-        <v>7.337883975</v>
+        <v>7.2828519</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1221525989828706</v>
+        <v>0.1230055100528311</v>
       </c>
       <c r="T29">
-        <v>0.7383879871115855</v>
+        <v>0.7466362890230196</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.636767991919057</v>
+        <v>3.50688342077909</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1014369672380384</v>
+        <v>0.1018982872185813</v>
       </c>
       <c r="C30">
-        <v>98.42450517118905</v>
+        <v>96.30450394906714</v>
       </c>
       <c r="D30">
-        <v>112.240505171189</v>
+        <v>111.3175039490671</v>
       </c>
       <c r="E30">
-        <v>10.916</v>
+        <v>12.113</v>
       </c>
       <c r="F30">
-        <v>33.516</v>
+        <v>34.713</v>
       </c>
       <c r="G30">
         <v>19.7</v>
@@ -3747,45 +3747,45 @@
         <v>7.205</v>
       </c>
       <c r="M30">
-        <v>2.0545308</v>
+        <v>2.2251033</v>
       </c>
       <c r="N30">
-        <v>5.1504692</v>
+        <v>4.979896699999999</v>
       </c>
       <c r="O30">
-        <v>1.2876173</v>
+        <v>1.244974175</v>
       </c>
       <c r="P30">
-        <v>3.8628519</v>
+        <v>3.734922525</v>
       </c>
       <c r="Q30">
-        <v>7.2828519</v>
+        <v>7.154922525</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1230055100528311</v>
+        <v>0.1238824467867342</v>
       </c>
       <c r="T30">
-        <v>0.7466362890230196</v>
+        <v>0.7551169374671701</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.50688342077909</v>
+        <v>3.238051914263935</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1018982872185813</v>
+        <v>0.1017716071991242</v>
       </c>
       <c r="C31">
-        <v>96.30450394906714</v>
+        <v>95.35944782332493</v>
       </c>
       <c r="D31">
-        <v>111.3175039490671</v>
+        <v>111.5694478233249</v>
       </c>
       <c r="E31">
-        <v>12.11299999999999</v>
+        <v>13.31</v>
       </c>
       <c r="F31">
-        <v>34.71299999999999</v>
+        <v>35.91</v>
       </c>
       <c r="G31">
         <v>19.7</v>
@@ -3829,28 +3829,28 @@
         <v>7.205</v>
       </c>
       <c r="M31">
-        <v>2.2251033</v>
+        <v>2.301831</v>
       </c>
       <c r="N31">
-        <v>4.9798967</v>
+        <v>4.903169</v>
       </c>
       <c r="O31">
-        <v>1.244974175</v>
+        <v>1.22579225</v>
       </c>
       <c r="P31">
-        <v>3.734922525</v>
+        <v>3.67737675</v>
       </c>
       <c r="Q31">
-        <v>7.154922525</v>
+        <v>7.09737675</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1238824467867342</v>
+        <v>0.1247844388558917</v>
       </c>
       <c r="T31">
-        <v>0.7551169374671701</v>
+        <v>0.7638398901525821</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.238051914263936</v>
+        <v>3.130116850455138</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1017716071991242</v>
+        <v>0.1016449271796671</v>
       </c>
       <c r="C32">
-        <v>95.35944782332493</v>
+        <v>94.41553472906313</v>
       </c>
       <c r="D32">
-        <v>111.5694478233249</v>
+        <v>111.8225347290631</v>
       </c>
       <c r="E32">
-        <v>13.31</v>
+        <v>14.507</v>
       </c>
       <c r="F32">
-        <v>35.91</v>
+        <v>37.107</v>
       </c>
       <c r="G32">
         <v>19.7</v>
@@ -3911,28 +3911,28 @@
         <v>7.205</v>
       </c>
       <c r="M32">
-        <v>2.301831</v>
+        <v>2.3785587</v>
       </c>
       <c r="N32">
-        <v>4.903169</v>
+        <v>4.8264413</v>
       </c>
       <c r="O32">
-        <v>1.22579225</v>
+        <v>1.206610325</v>
       </c>
       <c r="P32">
-        <v>3.67737675</v>
+        <v>3.619830975</v>
       </c>
       <c r="Q32">
-        <v>7.09737675</v>
+        <v>7.039830975</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1247844388558917</v>
+        <v>0.125712575622706</v>
       </c>
       <c r="T32">
-        <v>0.7638398901525821</v>
+        <v>0.772815682046267</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.130116850455138</v>
+        <v>3.029145339150133</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1016449271796671</v>
+        <v>0.10339024716021</v>
       </c>
       <c r="C33">
-        <v>94.41553472906313</v>
+        <v>89.82966050536589</v>
       </c>
       <c r="D33">
-        <v>111.8225347290631</v>
+        <v>108.4336605053659</v>
       </c>
       <c r="E33">
-        <v>14.507</v>
+        <v>15.70399999999999</v>
       </c>
       <c r="F33">
-        <v>37.107</v>
+        <v>38.30399999999999</v>
       </c>
       <c r="G33">
         <v>19.7</v>
@@ -3993,45 +3993,45 @@
         <v>7.205</v>
       </c>
       <c r="M33">
-        <v>2.3785587</v>
+        <v>2.7540576</v>
       </c>
       <c r="N33">
-        <v>4.8264413</v>
+        <v>4.450942400000001</v>
       </c>
       <c r="O33">
-        <v>1.206610325</v>
+        <v>1.1127356</v>
       </c>
       <c r="P33">
-        <v>3.619830975</v>
+        <v>3.3382068</v>
       </c>
       <c r="Q33">
-        <v>7.039830975</v>
+        <v>6.7582068</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.125712575622706</v>
+        <v>0.1266680105297207</v>
       </c>
       <c r="T33">
-        <v>0.772815682046267</v>
+        <v>0.782055467819178</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.029145339150133</v>
+        <v>2.616139909346849</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.10339024716021</v>
+        <v>0.1033220671407529</v>
       </c>
       <c r="C34">
-        <v>89.82966050536589</v>
+        <v>88.76118525161621</v>
       </c>
       <c r="D34">
-        <v>108.4336605053659</v>
+        <v>108.5621852516162</v>
       </c>
       <c r="E34">
-        <v>15.70399999999999</v>
+        <v>16.901</v>
       </c>
       <c r="F34">
-        <v>38.30399999999999</v>
+        <v>39.501</v>
       </c>
       <c r="G34">
         <v>19.7</v>
@@ -4075,28 +4075,28 @@
         <v>7.205</v>
       </c>
       <c r="M34">
-        <v>2.7540576</v>
+        <v>2.8401219</v>
       </c>
       <c r="N34">
-        <v>4.450942400000001</v>
+        <v>4.3648781</v>
       </c>
       <c r="O34">
-        <v>1.1127356</v>
+        <v>1.091219525</v>
       </c>
       <c r="P34">
-        <v>3.3382068</v>
+        <v>3.273658575</v>
       </c>
       <c r="Q34">
-        <v>6.7582068</v>
+        <v>6.693658575000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1266680105297207</v>
+        <v>0.1276519658817208</v>
       </c>
       <c r="T34">
-        <v>0.782055467819178</v>
+        <v>0.7915710680927728</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.616139909346849</v>
+        <v>2.536862942396944</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1033220671407529</v>
+        <v>0.1042483871212958</v>
       </c>
       <c r="C35">
-        <v>88.76118525161621</v>
+        <v>85.84363612643205</v>
       </c>
       <c r="D35">
-        <v>108.5621852516162</v>
+        <v>106.841636126432</v>
       </c>
       <c r="E35">
-        <v>16.901</v>
+        <v>18.098</v>
       </c>
       <c r="F35">
-        <v>39.501</v>
+        <v>40.698</v>
       </c>
       <c r="G35">
         <v>19.7</v>
@@ -4157,45 +4157,45 @@
         <v>7.205</v>
       </c>
       <c r="M35">
-        <v>2.8401219</v>
+        <v>3.0849084</v>
       </c>
       <c r="N35">
-        <v>4.3648781</v>
+        <v>4.1200916</v>
       </c>
       <c r="O35">
-        <v>1.091219525</v>
+        <v>1.0300229</v>
       </c>
       <c r="P35">
-        <v>3.273658575</v>
+        <v>3.0900687</v>
       </c>
       <c r="Q35">
-        <v>6.693658575000001</v>
+        <v>6.5100687</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1276519658817208</v>
+        <v>0.1286657380625695</v>
       </c>
       <c r="T35">
-        <v>0.7915710680927728</v>
+        <v>0.8013750198898099</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.536862942396944</v>
+        <v>2.335563675083513</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1042483871212958</v>
+        <v>0.1042094571018388</v>
       </c>
       <c r="C36">
-        <v>85.84363612643205</v>
+        <v>84.71784628964201</v>
       </c>
       <c r="D36">
-        <v>106.841636126432</v>
+        <v>106.912846289642</v>
       </c>
       <c r="E36">
-        <v>18.098</v>
+        <v>19.295</v>
       </c>
       <c r="F36">
-        <v>40.698</v>
+        <v>41.895</v>
       </c>
       <c r="G36">
         <v>19.7</v>
@@ -4239,28 +4239,28 @@
         <v>7.205</v>
       </c>
       <c r="M36">
-        <v>3.0849084</v>
+        <v>3.175641000000001</v>
       </c>
       <c r="N36">
-        <v>4.1200916</v>
+        <v>4.029358999999999</v>
       </c>
       <c r="O36">
-        <v>1.0300229</v>
+        <v>1.00733975</v>
       </c>
       <c r="P36">
-        <v>3.0900687</v>
+        <v>3.02201925</v>
       </c>
       <c r="Q36">
-        <v>6.5100687</v>
+        <v>6.44201925</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1286657380625695</v>
+        <v>0.1297107032335981</v>
       </c>
       <c r="T36">
-        <v>0.8013750198898099</v>
+        <v>0.8114806317421404</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.335563675083513</v>
+        <v>2.268833284366841</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1042094571018388</v>
+        <v>0.1041705270823816</v>
       </c>
       <c r="C37">
-        <v>84.71784628964201</v>
+        <v>83.59215143959204</v>
       </c>
       <c r="D37">
-        <v>106.912846289642</v>
+        <v>106.984151439592</v>
       </c>
       <c r="E37">
-        <v>19.295</v>
+        <v>20.492</v>
       </c>
       <c r="F37">
-        <v>41.895</v>
+        <v>43.092</v>
       </c>
       <c r="G37">
         <v>19.7</v>
@@ -4321,28 +4321,28 @@
         <v>7.205</v>
       </c>
       <c r="M37">
-        <v>3.175641000000001</v>
+        <v>3.2663736</v>
       </c>
       <c r="N37">
-        <v>4.029358999999999</v>
+        <v>3.9386264</v>
       </c>
       <c r="O37">
-        <v>1.00733975</v>
+        <v>0.9846566</v>
       </c>
       <c r="P37">
-        <v>3.02201925</v>
+        <v>2.9539698</v>
       </c>
       <c r="Q37">
-        <v>6.44201925</v>
+        <v>6.373969799999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1297107032335981</v>
+        <v>0.1307883235662213</v>
       </c>
       <c r="T37">
-        <v>0.8114806317421404</v>
+        <v>0.8219020439648561</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.268833284366841</v>
+        <v>2.205810137578873</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1041705270823817</v>
+        <v>0.1041315970629246</v>
       </c>
       <c r="C38">
-        <v>83.59215143959204</v>
+        <v>82.46655176646203</v>
       </c>
       <c r="D38">
-        <v>106.984151439592</v>
+        <v>107.055551766462</v>
       </c>
       <c r="E38">
-        <v>20.49199999999999</v>
+        <v>21.68899999999999</v>
       </c>
       <c r="F38">
-        <v>43.09199999999999</v>
+        <v>44.28899999999999</v>
       </c>
       <c r="G38">
         <v>19.7</v>
@@ -4403,28 +4403,28 @@
         <v>7.205</v>
       </c>
       <c r="M38">
-        <v>3.2663736</v>
+        <v>3.3571062</v>
       </c>
       <c r="N38">
-        <v>3.9386264</v>
+        <v>3.8478938</v>
       </c>
       <c r="O38">
-        <v>0.9846566000000001</v>
+        <v>0.96197345</v>
       </c>
       <c r="P38">
-        <v>2.9539698</v>
+        <v>2.88592035</v>
       </c>
       <c r="Q38">
-        <v>6.3739698</v>
+        <v>6.30592035</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1307883235662213</v>
+        <v>0.1319001540681342</v>
       </c>
       <c r="T38">
-        <v>0.8219020439648561</v>
+        <v>0.8326542946708329</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.205810137578874</v>
+        <v>2.146193647374039</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1041315970629246</v>
+        <v>0.1040926670434675</v>
       </c>
       <c r="C39">
-        <v>82.46655176646203</v>
+        <v>81.34104746094025</v>
       </c>
       <c r="D39">
-        <v>107.055551766462</v>
+        <v>107.1270474609402</v>
       </c>
       <c r="E39">
-        <v>21.68899999999999</v>
+        <v>22.886</v>
       </c>
       <c r="F39">
-        <v>44.28899999999999</v>
+        <v>45.486</v>
       </c>
       <c r="G39">
         <v>19.7</v>
@@ -4485,28 +4485,28 @@
         <v>7.205</v>
       </c>
       <c r="M39">
-        <v>3.3571062</v>
+        <v>3.4478388</v>
       </c>
       <c r="N39">
-        <v>3.8478938</v>
+        <v>3.7571612</v>
       </c>
       <c r="O39">
-        <v>0.96197345</v>
+        <v>0.9392903</v>
       </c>
       <c r="P39">
-        <v>2.88592035</v>
+        <v>2.8178709</v>
       </c>
       <c r="Q39">
-        <v>6.30592035</v>
+        <v>6.2378709</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1319001540681342</v>
+        <v>0.1330478500701088</v>
       </c>
       <c r="T39">
-        <v>0.8326542946708329</v>
+        <v>0.8437533921737765</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.146193647374039</v>
+        <v>2.089714867179985</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1040926670434675</v>
+        <v>0.1040537370240104</v>
       </c>
       <c r="C40">
-        <v>81.34104746094025</v>
+        <v>80.21563871422441</v>
       </c>
       <c r="D40">
-        <v>107.1270474609402</v>
+        <v>107.1986387142244</v>
       </c>
       <c r="E40">
-        <v>22.886</v>
+        <v>24.083</v>
       </c>
       <c r="F40">
-        <v>45.486</v>
+        <v>46.683</v>
       </c>
       <c r="G40">
         <v>19.7</v>
@@ -4567,28 +4567,28 @@
         <v>7.205</v>
       </c>
       <c r="M40">
-        <v>3.4478388</v>
+        <v>3.5385714</v>
       </c>
       <c r="N40">
-        <v>3.7571612</v>
+        <v>3.6664286</v>
       </c>
       <c r="O40">
-        <v>0.9392903</v>
+        <v>0.9166071499999999</v>
       </c>
       <c r="P40">
-        <v>2.8178709</v>
+        <v>2.74982145</v>
       </c>
       <c r="Q40">
-        <v>6.2378709</v>
+        <v>6.16982145</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1330478500701088</v>
+        <v>0.1342331754491974</v>
       </c>
       <c r="T40">
-        <v>0.8437533921737765</v>
+        <v>0.8552163945128822</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.089714867179985</v>
+        <v>2.036132434688191</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1040537370240104</v>
+        <v>0.1082748070045533</v>
       </c>
       <c r="C41">
-        <v>80.21563871422441</v>
+        <v>71.77583193294539</v>
       </c>
       <c r="D41">
-        <v>107.1986387142244</v>
+        <v>99.95583193294539</v>
       </c>
       <c r="E41">
-        <v>24.083</v>
+        <v>25.27999999999999</v>
       </c>
       <c r="F41">
-        <v>46.683</v>
+        <v>47.88</v>
       </c>
       <c r="G41">
         <v>19.7</v>
@@ -4649,45 +4649,45 @@
         <v>7.205</v>
       </c>
       <c r="M41">
-        <v>3.5385714</v>
+        <v>4.3092</v>
       </c>
       <c r="N41">
-        <v>3.6664286</v>
+        <v>2.8958</v>
       </c>
       <c r="O41">
-        <v>0.9166071499999999</v>
+        <v>0.7239500000000001</v>
       </c>
       <c r="P41">
-        <v>2.74982145</v>
+        <v>2.17185</v>
       </c>
       <c r="Q41">
-        <v>6.16982145</v>
+        <v>5.59185</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1342331754491974</v>
+        <v>0.1354580116742555</v>
       </c>
       <c r="T41">
-        <v>0.8552163945128822</v>
+        <v>0.8670614969299582</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.036132434688191</v>
+        <v>1.672004084284786</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1082748070045533</v>
+        <v>0.1083423769850962</v>
       </c>
       <c r="C42">
-        <v>71.77583193294539</v>
+        <v>70.47084093636924</v>
       </c>
       <c r="D42">
-        <v>99.95583193294539</v>
+        <v>99.84784093636924</v>
       </c>
       <c r="E42">
-        <v>25.27999999999999</v>
+        <v>26.477</v>
       </c>
       <c r="F42">
-        <v>47.88</v>
+        <v>49.077</v>
       </c>
       <c r="G42">
         <v>19.7</v>
@@ -4731,28 +4731,28 @@
         <v>7.205</v>
       </c>
       <c r="M42">
-        <v>4.3092</v>
+        <v>4.41693</v>
       </c>
       <c r="N42">
-        <v>2.8958</v>
+        <v>2.78807</v>
       </c>
       <c r="O42">
-        <v>0.7239500000000001</v>
+        <v>0.6970175000000001</v>
       </c>
       <c r="P42">
-        <v>2.17185</v>
+        <v>2.0910525</v>
       </c>
       <c r="Q42">
-        <v>5.59185</v>
+        <v>5.5110525</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1354580116742555</v>
+        <v>0.1367243677713495</v>
       </c>
       <c r="T42">
-        <v>0.8670614969299582</v>
+        <v>0.8793081282425282</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.672004084284786</v>
+        <v>1.631223496863206</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1083423769850962</v>
+        <v>0.1084099469656391</v>
       </c>
       <c r="C43">
-        <v>70.47084093636924</v>
+        <v>69.16608303213361</v>
       </c>
       <c r="D43">
-        <v>99.84784093636924</v>
+        <v>99.74008303213361</v>
       </c>
       <c r="E43">
-        <v>26.477</v>
+        <v>27.674</v>
       </c>
       <c r="F43">
-        <v>49.077</v>
+        <v>50.274</v>
       </c>
       <c r="G43">
         <v>19.7</v>
@@ -4813,28 +4813,28 @@
         <v>7.205</v>
       </c>
       <c r="M43">
-        <v>4.41693</v>
+        <v>4.52466</v>
       </c>
       <c r="N43">
-        <v>2.78807</v>
+        <v>2.68034</v>
       </c>
       <c r="O43">
-        <v>0.6970175000000001</v>
+        <v>0.670085</v>
       </c>
       <c r="P43">
-        <v>2.0910525</v>
+        <v>2.010255</v>
       </c>
       <c r="Q43">
-        <v>5.5110525</v>
+        <v>5.430255</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1367243677713495</v>
+        <v>0.1380343913200674</v>
       </c>
       <c r="T43">
-        <v>0.8793081282425282</v>
+        <v>0.8919770571865662</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.631223496863206</v>
+        <v>1.592384842175987</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1084099469656391</v>
+        <v>0.108477516946182</v>
       </c>
       <c r="C44">
-        <v>69.1660830321336</v>
+        <v>67.86155746637746</v>
       </c>
       <c r="D44">
-        <v>99.7400830321336</v>
+        <v>99.63255746637745</v>
       </c>
       <c r="E44">
-        <v>27.67399999999999</v>
+        <v>28.871</v>
       </c>
       <c r="F44">
-        <v>50.27399999999999</v>
+        <v>51.471</v>
       </c>
       <c r="G44">
         <v>19.7</v>
@@ -4895,28 +4895,28 @@
         <v>7.205</v>
       </c>
       <c r="M44">
-        <v>4.524659999999999</v>
+        <v>4.632389999999999</v>
       </c>
       <c r="N44">
-        <v>2.680340000000001</v>
+        <v>2.572610000000001</v>
       </c>
       <c r="O44">
-        <v>0.6700850000000003</v>
+        <v>0.6431525000000002</v>
       </c>
       <c r="P44">
-        <v>2.010255000000001</v>
+        <v>1.929457500000001</v>
       </c>
       <c r="Q44">
-        <v>5.430255000000001</v>
+        <v>5.349457500000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1380343913200674</v>
+        <v>0.1393903806073369</v>
       </c>
       <c r="T44">
-        <v>0.8919770571865662</v>
+        <v>0.9050905099532018</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.592384842175987</v>
+        <v>1.555352636543987</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.108477516946182</v>
+        <v>0.1085450869267249</v>
       </c>
       <c r="C45">
-        <v>67.86155746637746</v>
+        <v>66.55726348848712</v>
       </c>
       <c r="D45">
-        <v>99.63255746637745</v>
+        <v>99.52526348848711</v>
       </c>
       <c r="E45">
-        <v>28.871</v>
+        <v>30.06799999999999</v>
       </c>
       <c r="F45">
-        <v>51.471</v>
+        <v>52.66799999999999</v>
       </c>
       <c r="G45">
         <v>19.7</v>
@@ -4977,28 +4977,28 @@
         <v>7.205</v>
       </c>
       <c r="M45">
-        <v>4.632389999999999</v>
+        <v>4.740119999999999</v>
       </c>
       <c r="N45">
-        <v>2.572610000000001</v>
+        <v>2.464880000000001</v>
       </c>
       <c r="O45">
-        <v>0.6431525000000002</v>
+        <v>0.6162200000000002</v>
       </c>
       <c r="P45">
-        <v>1.929457500000001</v>
+        <v>1.848660000000001</v>
       </c>
       <c r="Q45">
-        <v>5.349457500000001</v>
+        <v>5.268660000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1393903806073369</v>
+        <v>0.1407947980834374</v>
       </c>
       <c r="T45">
-        <v>0.9050905099532018</v>
+        <v>0.9186723003186462</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.555352636543987</v>
+        <v>1.520003712986169</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1085450869267249</v>
+        <v>0.1298469180934207</v>
       </c>
       <c r="C46">
-        <v>66.55726348848712</v>
+        <v>40.13541993983796</v>
       </c>
       <c r="D46">
-        <v>99.52526348848711</v>
+        <v>74.30041993983795</v>
       </c>
       <c r="E46">
-        <v>30.06799999999999</v>
+        <v>31.26499999999999</v>
       </c>
       <c r="F46">
-        <v>52.66799999999999</v>
+        <v>53.86499999999999</v>
       </c>
       <c r="G46">
         <v>19.7</v>
@@ -5059,45 +5059,45 @@
         <v>7.205</v>
       </c>
       <c r="M46">
-        <v>4.740119999999999</v>
+        <v>7.907382</v>
       </c>
       <c r="N46">
-        <v>2.464880000000001</v>
+        <v>-0.7023820000000001</v>
       </c>
       <c r="O46">
-        <v>0.6162200000000002</v>
+        <v>-0.1755955</v>
       </c>
       <c r="P46">
-        <v>1.848660000000001</v>
+        <v>-0.5267865</v>
       </c>
       <c r="Q46">
-        <v>5.268660000000001</v>
+        <v>2.8932135</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1407947980834374</v>
+        <v>0.1433362815490614</v>
       </c>
       <c r="T46">
-        <v>0.9186723003186462</v>
+        <v>0.9432503878423014</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.25</v>
+        <v>0.2277934719734041</v>
       </c>
       <c r="W46">
-        <v>0.0675</v>
+        <v>0.1133599183143043</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.520003712986169</v>
+        <v>0.9111738878936164</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1298469180934207</v>
+        <v>0.1308569180934207</v>
       </c>
       <c r="C47">
-        <v>40.13541993983796</v>
+        <v>38.05614691817954</v>
       </c>
       <c r="D47">
-        <v>74.30041993983795</v>
+        <v>73.41814691817953</v>
       </c>
       <c r="E47">
-        <v>31.26499999999999</v>
+        <v>32.462</v>
       </c>
       <c r="F47">
-        <v>53.86499999999999</v>
+        <v>55.062</v>
       </c>
       <c r="G47">
         <v>19.7</v>
@@ -5141,37 +5141,37 @@
         <v>7.205</v>
       </c>
       <c r="M47">
-        <v>7.907382</v>
+        <v>8.083101600000001</v>
       </c>
       <c r="N47">
-        <v>-0.7023820000000001</v>
+        <v>-0.8781016000000008</v>
       </c>
       <c r="O47">
-        <v>-0.1755955</v>
+        <v>-0.2195254000000002</v>
       </c>
       <c r="P47">
-        <v>-0.5267865</v>
+        <v>-0.6585762000000006</v>
       </c>
       <c r="Q47">
-        <v>2.8932135</v>
+        <v>2.761423799999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1433362815490614</v>
+        <v>0.1451425089851552</v>
       </c>
       <c r="T47">
-        <v>0.9432503878423014</v>
+        <v>0.960717987617159</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2277934719734041</v>
+        <v>0.2228414399739822</v>
       </c>
       <c r="W47">
-        <v>0.1133599183143043</v>
+        <v>0.1140868766118194</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9111738878936164</v>
+        <v>0.8913657598959289</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1308569180934207</v>
+        <v>0.1318669180934207</v>
       </c>
       <c r="C48">
-        <v>38.05614691817954</v>
+        <v>35.99758094103052</v>
       </c>
       <c r="D48">
-        <v>73.41814691817953</v>
+        <v>72.55658094103052</v>
       </c>
       <c r="E48">
-        <v>32.462</v>
+        <v>33.659</v>
       </c>
       <c r="F48">
-        <v>55.062</v>
+        <v>56.259</v>
       </c>
       <c r="G48">
         <v>19.7</v>
@@ -5223,37 +5223,37 @@
         <v>7.205</v>
       </c>
       <c r="M48">
-        <v>8.083101600000001</v>
+        <v>8.258821200000002</v>
       </c>
       <c r="N48">
-        <v>-0.8781016000000008</v>
+        <v>-1.053821200000002</v>
       </c>
       <c r="O48">
-        <v>-0.2195254000000002</v>
+        <v>-0.2634553000000004</v>
       </c>
       <c r="P48">
-        <v>-0.6585762000000006</v>
+        <v>-0.7903659000000012</v>
       </c>
       <c r="Q48">
-        <v>2.761423799999999</v>
+        <v>2.629634099999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1451425089851552</v>
+        <v>0.1470168959471392</v>
       </c>
       <c r="T48">
-        <v>0.960717987617159</v>
+        <v>0.9788447421005014</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2228414399739822</v>
+        <v>0.2181001327404933</v>
       </c>
       <c r="W48">
-        <v>0.1140868766118194</v>
+        <v>0.1147829005136956</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8913657598959289</v>
+        <v>0.8724005309619729</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1318669180934207</v>
+        <v>0.1328769180934207</v>
       </c>
       <c r="C49">
-        <v>35.99758094103052</v>
+        <v>33.9590014690536</v>
       </c>
       <c r="D49">
-        <v>72.55658094103052</v>
+        <v>71.71500146905359</v>
       </c>
       <c r="E49">
-        <v>33.659</v>
+        <v>34.85599999999999</v>
       </c>
       <c r="F49">
-        <v>56.259</v>
+        <v>57.456</v>
       </c>
       <c r="G49">
         <v>19.7</v>
@@ -5305,37 +5305,37 @@
         <v>7.205</v>
       </c>
       <c r="M49">
-        <v>8.258821200000002</v>
+        <v>8.434540800000001</v>
       </c>
       <c r="N49">
-        <v>-1.053821200000002</v>
+        <v>-1.229540800000001</v>
       </c>
       <c r="O49">
-        <v>-0.2634553000000004</v>
+        <v>-0.3073852000000001</v>
       </c>
       <c r="P49">
-        <v>-0.7903659000000012</v>
+        <v>-0.9221556000000004</v>
       </c>
       <c r="Q49">
-        <v>2.629634099999999</v>
+        <v>2.4978444</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1470168959471392</v>
+        <v>0.1489633747153535</v>
       </c>
       <c r="T49">
-        <v>0.9788447421005014</v>
+        <v>0.9976686794485881</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2181001327404933</v>
+        <v>0.2135563799750663</v>
       </c>
       <c r="W49">
-        <v>0.1147829005136956</v>
+        <v>0.1154499234196603</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8724005309619729</v>
+        <v>0.8542255199002653</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1328769180934207</v>
+        <v>0.1338869180934207</v>
       </c>
       <c r="C50">
-        <v>33.9590014690536</v>
+        <v>31.93972100957689</v>
       </c>
       <c r="D50">
-        <v>71.71500146905359</v>
+        <v>70.89272100957687</v>
       </c>
       <c r="E50">
-        <v>34.85599999999999</v>
+        <v>36.05299999999999</v>
       </c>
       <c r="F50">
-        <v>57.456</v>
+        <v>58.65299999999999</v>
       </c>
       <c r="G50">
         <v>19.7</v>
@@ -5387,37 +5387,37 @@
         <v>7.205</v>
       </c>
       <c r="M50">
-        <v>8.434540800000001</v>
+        <v>8.6102604</v>
       </c>
       <c r="N50">
-        <v>-1.229540800000001</v>
+        <v>-1.4052604</v>
       </c>
       <c r="O50">
-        <v>-0.3073852000000001</v>
+        <v>-0.3513150999999999</v>
       </c>
       <c r="P50">
-        <v>-0.9221556000000004</v>
+        <v>-1.0539453</v>
       </c>
       <c r="Q50">
-        <v>2.4978444</v>
+        <v>2.3660547</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1489633747153535</v>
+        <v>0.150986185984282</v>
       </c>
       <c r="T50">
-        <v>0.9976686794485879</v>
+        <v>1.017230810418168</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2135563799750663</v>
+        <v>0.2091980865061874</v>
       </c>
       <c r="W50">
-        <v>0.1154499234196603</v>
+        <v>0.1160897209008917</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8542255199002653</v>
+        <v>0.8367923460247497</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1338869180934207</v>
+        <v>0.1348969180934207</v>
       </c>
       <c r="C51">
-        <v>31.93972100957689</v>
+        <v>29.93908324351415</v>
       </c>
       <c r="D51">
-        <v>70.89272100957687</v>
+        <v>70.08908324351414</v>
       </c>
       <c r="E51">
-        <v>36.05299999999999</v>
+        <v>37.24999999999999</v>
       </c>
       <c r="F51">
-        <v>58.65299999999999</v>
+        <v>59.84999999999999</v>
       </c>
       <c r="G51">
         <v>19.7</v>
@@ -5469,37 +5469,37 @@
         <v>7.205</v>
       </c>
       <c r="M51">
-        <v>8.6102604</v>
+        <v>8.78598</v>
       </c>
       <c r="N51">
-        <v>-1.4052604</v>
+        <v>-1.58098</v>
       </c>
       <c r="O51">
-        <v>-0.3513150999999999</v>
+        <v>-0.3952450000000001</v>
       </c>
       <c r="P51">
-        <v>-1.0539453</v>
+        <v>-1.185735</v>
       </c>
       <c r="Q51">
-        <v>2.3660547</v>
+        <v>2.234265</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.150986185984282</v>
+        <v>0.1530899097039676</v>
       </c>
       <c r="T51">
-        <v>1.017230810418168</v>
+        <v>1.037575426626532</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2091980865061874</v>
+        <v>0.2050141247760637</v>
       </c>
       <c r="W51">
-        <v>0.1160897209008917</v>
+        <v>0.1167039264828739</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8367923460247497</v>
+        <v>0.8200564991042547</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1348969180934207</v>
+        <v>0.1359069180934207</v>
       </c>
       <c r="C52">
-        <v>29.93908324351415</v>
+        <v>27.95646127825553</v>
       </c>
       <c r="D52">
-        <v>70.08908324351414</v>
+        <v>69.30346127825553</v>
       </c>
       <c r="E52">
-        <v>37.24999999999999</v>
+        <v>38.447</v>
       </c>
       <c r="F52">
-        <v>59.84999999999999</v>
+        <v>61.047</v>
       </c>
       <c r="G52">
         <v>19.7</v>
@@ -5551,37 +5551,37 @@
         <v>7.205</v>
       </c>
       <c r="M52">
-        <v>8.78598</v>
+        <v>8.961699600000001</v>
       </c>
       <c r="N52">
-        <v>-1.58098</v>
+        <v>-1.756699600000001</v>
       </c>
       <c r="O52">
-        <v>-0.3952450000000001</v>
+        <v>-0.4391749000000003</v>
       </c>
       <c r="P52">
-        <v>-1.185735</v>
+        <v>-1.317524700000001</v>
       </c>
       <c r="Q52">
-        <v>2.234265</v>
+        <v>2.102475299999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1530899097039676</v>
+        <v>0.1552794996979261</v>
       </c>
       <c r="T52">
-        <v>1.037575426626532</v>
+        <v>1.058750435333196</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2050141247760637</v>
+        <v>0.200994239976533</v>
       </c>
       <c r="W52">
-        <v>0.1167039264828739</v>
+        <v>0.117294045571445</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8200564991042547</v>
+        <v>0.8039769599061319</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1359069180934207</v>
+        <v>0.1666446315310008</v>
       </c>
       <c r="C53">
-        <v>27.95646127825553</v>
+        <v>9.131620421651441</v>
       </c>
       <c r="D53">
-        <v>69.30346127825553</v>
+        <v>51.67562042165143</v>
       </c>
       <c r="E53">
-        <v>38.447</v>
+        <v>39.64399999999999</v>
       </c>
       <c r="F53">
-        <v>61.047</v>
+        <v>62.24399999999999</v>
       </c>
       <c r="G53">
         <v>19.7</v>
@@ -5633,45 +5633,45 @@
         <v>7.205</v>
       </c>
       <c r="M53">
-        <v>8.961699600000001</v>
+        <v>12.4985952</v>
       </c>
       <c r="N53">
-        <v>-1.756699600000001</v>
+        <v>-5.293595199999999</v>
       </c>
       <c r="O53">
-        <v>-0.4391749000000003</v>
+        <v>-1.3233988</v>
       </c>
       <c r="P53">
-        <v>-1.317524700000001</v>
+        <v>-3.970196399999999</v>
       </c>
       <c r="Q53">
-        <v>2.102475299999999</v>
+        <v>-0.550196399999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1552794996979261</v>
+        <v>0.1609930589365913</v>
       </c>
       <c r="T53">
-        <v>1.058750435333196</v>
+        <v>1.114004919943828</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.200994239976533</v>
+        <v>0.1441161963546111</v>
       </c>
       <c r="W53">
-        <v>0.117294045571445</v>
+        <v>0.1718614677719941</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8039769599061319</v>
+        <v>0.5764647854184446</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1666446315310008</v>
+        <v>0.1681946315310008</v>
       </c>
       <c r="C54">
-        <v>9.131620421651441</v>
+        <v>7.280202734767236</v>
       </c>
       <c r="D54">
-        <v>51.67562042165143</v>
+        <v>51.02120273476724</v>
       </c>
       <c r="E54">
-        <v>39.64399999999999</v>
+        <v>40.84099999999999</v>
       </c>
       <c r="F54">
-        <v>62.24399999999999</v>
+        <v>63.441</v>
       </c>
       <c r="G54">
         <v>19.7</v>
@@ -5715,37 +5715,37 @@
         <v>7.205</v>
       </c>
       <c r="M54">
-        <v>12.4985952</v>
+        <v>12.7389528</v>
       </c>
       <c r="N54">
-        <v>-5.293595199999999</v>
+        <v>-5.5339528</v>
       </c>
       <c r="O54">
-        <v>-1.3233988</v>
+        <v>-1.3834882</v>
       </c>
       <c r="P54">
-        <v>-3.970196399999999</v>
+        <v>-4.150464599999999</v>
       </c>
       <c r="Q54">
-        <v>-0.550196399999999</v>
+        <v>-0.7304645999999995</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1609930589365913</v>
+        <v>0.1634439750841784</v>
       </c>
       <c r="T54">
-        <v>1.114004919943828</v>
+        <v>1.137707152283058</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1441161963546111</v>
+        <v>0.1413970228384864</v>
       </c>
       <c r="W54">
-        <v>0.1718614677719941</v>
+        <v>0.1724074778140319</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5764647854184446</v>
+        <v>0.5655880913539455</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1681946315310008</v>
+        <v>0.1697446315310008</v>
       </c>
       <c r="C55">
-        <v>7.280202734767236</v>
+        <v>5.445152798581759</v>
       </c>
       <c r="D55">
-        <v>51.02120273476724</v>
+        <v>50.38315279858175</v>
       </c>
       <c r="E55">
-        <v>40.84099999999999</v>
+        <v>42.03799999999999</v>
       </c>
       <c r="F55">
-        <v>63.441</v>
+        <v>64.63799999999999</v>
       </c>
       <c r="G55">
         <v>19.7</v>
@@ -5797,37 +5797,37 @@
         <v>7.205</v>
       </c>
       <c r="M55">
-        <v>12.7389528</v>
+        <v>12.9793104</v>
       </c>
       <c r="N55">
-        <v>-5.5339528</v>
+        <v>-5.774310399999999</v>
       </c>
       <c r="O55">
-        <v>-1.3834882</v>
+        <v>-1.4435776</v>
       </c>
       <c r="P55">
-        <v>-4.150464599999999</v>
+        <v>-4.3307328</v>
       </c>
       <c r="Q55">
-        <v>-0.7304645999999995</v>
+        <v>-0.9107327999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1634439750841784</v>
+        <v>0.1660014528033997</v>
       </c>
       <c r="T55">
-        <v>1.137707152283058</v>
+        <v>1.162439916463125</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1413970228384864</v>
+        <v>0.1387785594525885</v>
       </c>
       <c r="W55">
-        <v>0.1724074778140319</v>
+        <v>0.1729332652619202</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5655880913539455</v>
+        <v>0.555114237810354</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1697446315310008</v>
+        <v>0.1712946315310008</v>
       </c>
       <c r="C56">
-        <v>5.445152798581759</v>
+        <v>3.625864132643812</v>
       </c>
       <c r="D56">
-        <v>50.38315279858175</v>
+        <v>49.7608641326438</v>
       </c>
       <c r="E56">
-        <v>42.03799999999999</v>
+        <v>43.23499999999999</v>
       </c>
       <c r="F56">
-        <v>64.63799999999999</v>
+        <v>65.83499999999999</v>
       </c>
       <c r="G56">
         <v>19.7</v>
@@ -5879,37 +5879,37 @@
         <v>7.205</v>
       </c>
       <c r="M56">
-        <v>12.9793104</v>
+        <v>13.219668</v>
       </c>
       <c r="N56">
-        <v>-5.774310399999999</v>
+        <v>-6.014667999999999</v>
       </c>
       <c r="O56">
-        <v>-1.4435776</v>
+        <v>-1.503667</v>
       </c>
       <c r="P56">
-        <v>-4.3307328</v>
+        <v>-4.511000999999998</v>
       </c>
       <c r="Q56">
-        <v>-0.9107327999999999</v>
+        <v>-1.091000999999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1660014528033997</v>
+        <v>0.1686725961990307</v>
       </c>
       <c r="T56">
-        <v>1.162439916463125</v>
+        <v>1.18827191460675</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1387785594525885</v>
+        <v>0.1362553129170869</v>
       </c>
       <c r="W56">
-        <v>0.1729332652619202</v>
+        <v>0.1734399331662489</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.555114237810354</v>
+        <v>0.5450212516683476</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1712946315310008</v>
+        <v>0.1728446315310008</v>
       </c>
       <c r="C57">
-        <v>3.625864132643812</v>
+        <v>1.821759853807933</v>
       </c>
       <c r="D57">
-        <v>49.7608641326438</v>
+        <v>49.15375985380793</v>
       </c>
       <c r="E57">
-        <v>43.23499999999999</v>
+        <v>44.432</v>
       </c>
       <c r="F57">
-        <v>65.83499999999999</v>
+        <v>67.032</v>
       </c>
       <c r="G57">
         <v>19.7</v>
@@ -5961,37 +5961,37 @@
         <v>7.205</v>
       </c>
       <c r="M57">
-        <v>13.219668</v>
+        <v>13.4600256</v>
       </c>
       <c r="N57">
-        <v>-6.014667999999999</v>
+        <v>-6.2550256</v>
       </c>
       <c r="O57">
-        <v>-1.503667</v>
+        <v>-1.5637564</v>
       </c>
       <c r="P57">
-        <v>-4.511000999999998</v>
+        <v>-4.6912692</v>
       </c>
       <c r="Q57">
-        <v>-1.091000999999999</v>
+        <v>-1.2712692</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1686725961990307</v>
+        <v>0.1714651552035542</v>
       </c>
       <c r="T57">
-        <v>1.18827191460675</v>
+        <v>1.215278094484176</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1362553129170869</v>
+        <v>0.1338221823292818</v>
       </c>
       <c r="W57">
-        <v>0.1734399331662489</v>
+        <v>0.1739285057882802</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5450212516683476</v>
+        <v>0.535288729317127</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1728446315310008</v>
+        <v>0.1743946315310008</v>
       </c>
       <c r="C58">
-        <v>1.821759853807933</v>
+        <v>0.03229089249646222</v>
       </c>
       <c r="D58">
-        <v>49.15375985380793</v>
+        <v>48.56129089249646</v>
       </c>
       <c r="E58">
-        <v>44.432</v>
+        <v>45.629</v>
       </c>
       <c r="F58">
-        <v>67.032</v>
+        <v>68.229</v>
       </c>
       <c r="G58">
         <v>19.7</v>
@@ -6043,37 +6043,37 @@
         <v>7.205</v>
       </c>
       <c r="M58">
-        <v>13.4600256</v>
+        <v>13.7003832</v>
       </c>
       <c r="N58">
-        <v>-6.2550256</v>
+        <v>-6.495383200000001</v>
       </c>
       <c r="O58">
-        <v>-1.5637564</v>
+        <v>-1.6238458</v>
       </c>
       <c r="P58">
-        <v>-4.6912692</v>
+        <v>-4.871537400000001</v>
       </c>
       <c r="Q58">
-        <v>-1.2712692</v>
+        <v>-1.451537400000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1714651552035542</v>
+        <v>0.1743876006734043</v>
       </c>
       <c r="T58">
-        <v>1.215278094484176</v>
+        <v>1.24354037575125</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1338221823292818</v>
+        <v>0.1314744247445575</v>
       </c>
       <c r="W58">
-        <v>0.1739285057882802</v>
+        <v>0.1743999355112928</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.535288729317127</v>
+        <v>0.52589769897823</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1743946315310008</v>
+        <v>0.1759446315310008</v>
       </c>
       <c r="C59">
-        <v>0.03229089249646222</v>
+        <v>-1.743065663574313</v>
       </c>
       <c r="D59">
-        <v>48.56129089249646</v>
+        <v>47.98293433642569</v>
       </c>
       <c r="E59">
-        <v>45.629</v>
+        <v>46.826</v>
       </c>
       <c r="F59">
-        <v>68.229</v>
+        <v>69.426</v>
       </c>
       <c r="G59">
         <v>19.7</v>
@@ -6125,37 +6125,37 @@
         <v>7.205</v>
       </c>
       <c r="M59">
-        <v>13.7003832</v>
+        <v>13.9407408</v>
       </c>
       <c r="N59">
-        <v>-6.495383200000001</v>
+        <v>-6.7357408</v>
       </c>
       <c r="O59">
-        <v>-1.6238458</v>
+        <v>-1.6839352</v>
       </c>
       <c r="P59">
-        <v>-4.871537400000001</v>
+        <v>-5.0518056</v>
       </c>
       <c r="Q59">
-        <v>-1.451537400000001</v>
+        <v>-1.6318056</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1743876006734043</v>
+        <v>0.1774492102132472</v>
       </c>
       <c r="T59">
-        <v>1.24354037575125</v>
+        <v>1.273148479935803</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1314744247445575</v>
+        <v>0.1292076243179272</v>
       </c>
       <c r="W59">
-        <v>0.1743999355112928</v>
+        <v>0.1748551090369602</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.52589769897823</v>
+        <v>0.5168304972717088</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1759446315310008</v>
+        <v>0.1774946315310008</v>
       </c>
       <c r="C60">
-        <v>-1.743065663574299</v>
+        <v>-3.504808108705419</v>
       </c>
       <c r="D60">
-        <v>47.98293433642569</v>
+        <v>47.41819189129458</v>
       </c>
       <c r="E60">
-        <v>46.82599999999999</v>
+        <v>48.02299999999999</v>
       </c>
       <c r="F60">
-        <v>69.42599999999999</v>
+        <v>70.62299999999999</v>
       </c>
       <c r="G60">
         <v>19.7</v>
@@ -6207,37 +6207,37 @@
         <v>7.205</v>
       </c>
       <c r="M60">
-        <v>13.9407408</v>
+        <v>14.1810984</v>
       </c>
       <c r="N60">
-        <v>-6.735740799999999</v>
+        <v>-6.976098399999998</v>
       </c>
       <c r="O60">
-        <v>-1.6839352</v>
+        <v>-1.744024599999999</v>
       </c>
       <c r="P60">
-        <v>-5.051805599999999</v>
+        <v>-5.232073799999998</v>
       </c>
       <c r="Q60">
-        <v>-1.631805599999999</v>
+        <v>-1.812073799999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1774492102132472</v>
+        <v>0.1806601665599118</v>
       </c>
       <c r="T60">
-        <v>1.273148479935803</v>
+        <v>1.304200881885457</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1292076243179272</v>
+        <v>0.1270176645837251</v>
       </c>
       <c r="W60">
-        <v>0.1748551090369602</v>
+        <v>0.175294852951588</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5168304972717088</v>
+        <v>0.5080706583349003</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1774946315310008</v>
+        <v>0.2007095038052355</v>
       </c>
       <c r="C61">
-        <v>-3.504808108705419</v>
+        <v>-11.80793937367662</v>
       </c>
       <c r="D61">
-        <v>47.41819189129458</v>
+        <v>40.31206062632338</v>
       </c>
       <c r="E61">
-        <v>48.02299999999999</v>
+        <v>49.21999999999999</v>
       </c>
       <c r="F61">
-        <v>70.62299999999999</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="G61">
         <v>19.7</v>
@@ -6289,45 +6289,45 @@
         <v>7.205</v>
       </c>
       <c r="M61">
-        <v>14.1810984</v>
+        <v>16.935156</v>
       </c>
       <c r="N61">
-        <v>-6.976098399999998</v>
+        <v>-9.730155999999999</v>
       </c>
       <c r="O61">
-        <v>-1.744024599999999</v>
+        <v>-2.432539</v>
       </c>
       <c r="P61">
-        <v>-5.232073799999998</v>
+        <v>-7.297616999999999</v>
       </c>
       <c r="Q61">
-        <v>-1.812073799999999</v>
+        <v>-3.877616999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1806601665599118</v>
+        <v>0.1856938514094965</v>
       </c>
       <c r="T61">
-        <v>1.304200881885457</v>
+        <v>1.352880461537655</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1270176645837251</v>
+        <v>0.1063615829697701</v>
       </c>
       <c r="W61">
-        <v>0.175294852951588</v>
+        <v>0.2107199387357282</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5080706583349003</v>
+        <v>0.4254463318790804</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2007095038052355</v>
+        <v>0.2026095038052355</v>
       </c>
       <c r="C62">
-        <v>-11.80793937367662</v>
+        <v>-13.49338499292395</v>
       </c>
       <c r="D62">
-        <v>40.31206062632338</v>
+        <v>39.82361500707604</v>
       </c>
       <c r="E62">
-        <v>49.21999999999999</v>
+        <v>50.41699999999999</v>
       </c>
       <c r="F62">
-        <v>71.81999999999999</v>
+        <v>73.017</v>
       </c>
       <c r="G62">
         <v>19.7</v>
@@ -6371,37 +6371,37 @@
         <v>7.205</v>
       </c>
       <c r="M62">
-        <v>16.935156</v>
+        <v>17.2174086</v>
       </c>
       <c r="N62">
-        <v>-9.730155999999999</v>
+        <v>-10.0124086</v>
       </c>
       <c r="O62">
-        <v>-2.432539</v>
+        <v>-2.50310215</v>
       </c>
       <c r="P62">
-        <v>-7.297616999999999</v>
+        <v>-7.509306449999999</v>
       </c>
       <c r="Q62">
-        <v>-3.877616999999999</v>
+        <v>-4.089306449999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1856938514094965</v>
+        <v>0.1892808732405093</v>
       </c>
       <c r="T62">
-        <v>1.352880461537655</v>
+        <v>1.387569704141184</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1063615829697701</v>
+        <v>0.104617950462069</v>
       </c>
       <c r="W62">
-        <v>0.2107199387357282</v>
+        <v>0.2111310872810441</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4254463318790804</v>
+        <v>0.4184718018482758</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2026095038052355</v>
+        <v>0.2045095038052355</v>
       </c>
       <c r="C63">
-        <v>-13.49338499292395</v>
+        <v>-15.16713570223433</v>
       </c>
       <c r="D63">
-        <v>39.82361500707604</v>
+        <v>39.34686429776566</v>
       </c>
       <c r="E63">
-        <v>50.41699999999999</v>
+        <v>51.614</v>
       </c>
       <c r="F63">
-        <v>73.017</v>
+        <v>74.214</v>
       </c>
       <c r="G63">
         <v>19.7</v>
@@ -6453,37 +6453,37 @@
         <v>7.205</v>
       </c>
       <c r="M63">
-        <v>17.2174086</v>
+        <v>17.4996612</v>
       </c>
       <c r="N63">
-        <v>-10.0124086</v>
+        <v>-10.2946612</v>
       </c>
       <c r="O63">
-        <v>-2.50310215</v>
+        <v>-2.5736653</v>
       </c>
       <c r="P63">
-        <v>-7.509306449999999</v>
+        <v>-7.720995900000002</v>
       </c>
       <c r="Q63">
-        <v>-4.089306449999999</v>
+        <v>-4.300995900000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1892808732405093</v>
+        <v>0.1930566856942069</v>
       </c>
       <c r="T63">
-        <v>1.387569704141184</v>
+        <v>1.424084696355426</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.104617950462069</v>
+        <v>0.1029305641642936</v>
       </c>
       <c r="W63">
-        <v>0.2111310872810441</v>
+        <v>0.2115289729700595</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4184718018482758</v>
+        <v>0.4117222566571745</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2045095038052355</v>
+        <v>0.2064095038052355</v>
       </c>
       <c r="C64">
-        <v>-15.16713570223433</v>
+        <v>-16.82960655168301</v>
       </c>
       <c r="D64">
-        <v>39.34686429776566</v>
+        <v>38.88139344831698</v>
       </c>
       <c r="E64">
-        <v>51.614</v>
+        <v>52.81099999999999</v>
       </c>
       <c r="F64">
-        <v>74.214</v>
+        <v>75.41099999999999</v>
       </c>
       <c r="G64">
         <v>19.7</v>
@@ -6535,37 +6535,37 @@
         <v>7.205</v>
       </c>
       <c r="M64">
-        <v>17.4996612</v>
+        <v>17.7819138</v>
       </c>
       <c r="N64">
-        <v>-10.2946612</v>
+        <v>-10.5769138</v>
       </c>
       <c r="O64">
-        <v>-2.5736653</v>
+        <v>-2.64422845</v>
       </c>
       <c r="P64">
-        <v>-7.720995900000002</v>
+        <v>-7.932685349999998</v>
       </c>
       <c r="Q64">
-        <v>-4.300995900000002</v>
+        <v>-4.512685349999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1930566856942069</v>
+        <v>0.1970365961183747</v>
       </c>
       <c r="T64">
-        <v>1.424084696355426</v>
+        <v>1.4625734719326</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1029305641642936</v>
+        <v>0.1012967456854953</v>
       </c>
       <c r="W64">
-        <v>0.2115289729700595</v>
+        <v>0.2119142273673602</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4117222566571745</v>
+        <v>0.4051869827419814</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2064095038052355</v>
+        <v>0.2083095038052356</v>
       </c>
       <c r="C65">
-        <v>-16.82960655168301</v>
+        <v>-18.48119318090772</v>
       </c>
       <c r="D65">
-        <v>38.88139344831698</v>
+        <v>38.42680681909227</v>
       </c>
       <c r="E65">
-        <v>52.81099999999999</v>
+        <v>54.00799999999999</v>
       </c>
       <c r="F65">
-        <v>75.41099999999999</v>
+        <v>76.60799999999999</v>
       </c>
       <c r="G65">
         <v>19.7</v>
@@ -6617,37 +6617,37 @@
         <v>7.205</v>
       </c>
       <c r="M65">
-        <v>17.7819138</v>
+        <v>18.0641664</v>
       </c>
       <c r="N65">
-        <v>-10.5769138</v>
+        <v>-10.8591664</v>
       </c>
       <c r="O65">
-        <v>-2.64422845</v>
+        <v>-2.714791599999999</v>
       </c>
       <c r="P65">
-        <v>-7.932685349999998</v>
+        <v>-8.144374799999998</v>
       </c>
       <c r="Q65">
-        <v>-4.512685349999998</v>
+        <v>-4.724374799999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1970365961183747</v>
+        <v>0.2012376126772184</v>
       </c>
       <c r="T65">
-        <v>1.4625734719326</v>
+        <v>1.503200512819616</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1012967456854953</v>
+        <v>0.09971398403415949</v>
       </c>
       <c r="W65">
-        <v>0.2119142273673602</v>
+        <v>0.2122874425647452</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4051869827419814</v>
+        <v>0.3988559361366379</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2083095038052356</v>
+        <v>0.2102095038052356</v>
       </c>
       <c r="C66">
-        <v>-18.48119318090772</v>
+        <v>-20.12227294069319</v>
       </c>
       <c r="D66">
-        <v>38.42680681909227</v>
+        <v>37.9827270593068</v>
       </c>
       <c r="E66">
-        <v>54.00799999999999</v>
+        <v>55.20499999999999</v>
       </c>
       <c r="F66">
-        <v>76.60799999999999</v>
+        <v>77.80499999999999</v>
       </c>
       <c r="G66">
         <v>19.7</v>
@@ -6699,37 +6699,37 @@
         <v>7.205</v>
       </c>
       <c r="M66">
-        <v>18.0641664</v>
+        <v>18.346419</v>
       </c>
       <c r="N66">
-        <v>-10.8591664</v>
+        <v>-11.141419</v>
       </c>
       <c r="O66">
-        <v>-2.714791599999999</v>
+        <v>-2.785354749999999</v>
       </c>
       <c r="P66">
-        <v>-8.144374799999998</v>
+        <v>-8.356064249999998</v>
       </c>
       <c r="Q66">
-        <v>-4.724374799999998</v>
+        <v>-4.936064249999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2012376126772184</v>
+        <v>0.2056786873251389</v>
       </c>
       <c r="T66">
-        <v>1.503200512819616</v>
+        <v>1.546149098900177</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09971398403415949</v>
+        <v>0.09817992274132627</v>
       </c>
       <c r="W66">
-        <v>0.2122874425647452</v>
+        <v>0.2126491742175953</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3988559361366379</v>
+        <v>0.392719690965305</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2102095038052356</v>
+        <v>0.2121095038052355</v>
       </c>
       <c r="C67">
-        <v>-20.12227294069319</v>
+        <v>-21.75320593767452</v>
       </c>
       <c r="D67">
-        <v>37.9827270593068</v>
+        <v>37.54879406232548</v>
       </c>
       <c r="E67">
-        <v>55.20499999999999</v>
+        <v>56.40199999999999</v>
       </c>
       <c r="F67">
-        <v>77.80499999999999</v>
+        <v>79.002</v>
       </c>
       <c r="G67">
         <v>19.7</v>
@@ -6781,37 +6781,37 @@
         <v>7.205</v>
       </c>
       <c r="M67">
-        <v>18.346419</v>
+        <v>18.6286716</v>
       </c>
       <c r="N67">
-        <v>-11.141419</v>
+        <v>-11.4236716</v>
       </c>
       <c r="O67">
-        <v>-2.785354749999999</v>
+        <v>-2.8559179</v>
       </c>
       <c r="P67">
-        <v>-8.356064249999998</v>
+        <v>-8.567753700000001</v>
       </c>
       <c r="Q67">
-        <v>-4.936064249999998</v>
+        <v>-5.147753700000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2056786873251389</v>
+        <v>0.2103810016582313</v>
       </c>
       <c r="T67">
-        <v>1.546149098900177</v>
+        <v>1.591624072397241</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09817992274132627</v>
+        <v>0.09669234815433646</v>
       </c>
       <c r="W67">
-        <v>0.2126491742175953</v>
+        <v>0.2129999443052075</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.392719690965305</v>
+        <v>0.3867693926173458</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2121095038052355</v>
+        <v>0.2140095038052356</v>
       </c>
       <c r="C68">
-        <v>-21.75320593767452</v>
+        <v>-23.37433600823834</v>
       </c>
       <c r="D68">
-        <v>37.54879406232548</v>
+        <v>37.12466399176166</v>
       </c>
       <c r="E68">
-        <v>56.40199999999999</v>
+        <v>57.599</v>
       </c>
       <c r="F68">
-        <v>79.002</v>
+        <v>80.199</v>
       </c>
       <c r="G68">
         <v>19.7</v>
@@ -6863,37 +6863,37 @@
         <v>7.205</v>
       </c>
       <c r="M68">
-        <v>18.6286716</v>
+        <v>18.9109242</v>
       </c>
       <c r="N68">
-        <v>-11.4236716</v>
+        <v>-11.7059242</v>
       </c>
       <c r="O68">
-        <v>-2.8559179</v>
+        <v>-2.92648105</v>
       </c>
       <c r="P68">
-        <v>-8.567753700000001</v>
+        <v>-8.779443150000001</v>
       </c>
       <c r="Q68">
-        <v>-5.147753700000001</v>
+        <v>-5.359443150000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2103810016582313</v>
+        <v>0.2153683047387837</v>
       </c>
       <c r="T68">
-        <v>1.591624072397241</v>
+        <v>1.639855104894127</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09669234815433646</v>
+        <v>0.0952491787788986</v>
       </c>
       <c r="W68">
-        <v>0.2129999443052075</v>
+        <v>0.2133402436439357</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3867693926173458</v>
+        <v>0.3809967151155944</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2140095038052356</v>
+        <v>0.2159095038052355</v>
       </c>
       <c r="C69">
-        <v>-23.37433600823834</v>
+        <v>-24.98599162715723</v>
       </c>
       <c r="D69">
-        <v>37.12466399176166</v>
+        <v>36.71000837284276</v>
       </c>
       <c r="E69">
-        <v>57.599</v>
+        <v>58.796</v>
       </c>
       <c r="F69">
-        <v>80.199</v>
+        <v>81.396</v>
       </c>
       <c r="G69">
         <v>19.7</v>
@@ -6945,37 +6945,37 @@
         <v>7.205</v>
       </c>
       <c r="M69">
-        <v>18.9109242</v>
+        <v>19.1931768</v>
       </c>
       <c r="N69">
-        <v>-11.7059242</v>
+        <v>-11.9881768</v>
       </c>
       <c r="O69">
-        <v>-2.92648105</v>
+        <v>-2.9970442</v>
       </c>
       <c r="P69">
-        <v>-8.779443150000001</v>
+        <v>-8.9911326</v>
       </c>
       <c r="Q69">
-        <v>-5.359443150000001</v>
+        <v>-5.5711326</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2153683047387837</v>
+        <v>0.2206673142618707</v>
       </c>
       <c r="T69">
-        <v>1.639855104894127</v>
+        <v>1.691100576922069</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0952491787788986</v>
+        <v>0.09384845556156186</v>
       </c>
       <c r="W69">
-        <v>0.2133402436439357</v>
+        <v>0.2136705341785837</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3809967151155944</v>
+        <v>0.3753938222462474</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2159095038052355</v>
+        <v>0.2178095038052356</v>
       </c>
       <c r="C70">
-        <v>-24.98599162715723</v>
+        <v>-26.58848675600417</v>
       </c>
       <c r="D70">
-        <v>36.71000837284276</v>
+        <v>36.30451324399584</v>
       </c>
       <c r="E70">
-        <v>58.796</v>
+        <v>59.993</v>
       </c>
       <c r="F70">
-        <v>81.396</v>
+        <v>82.593</v>
       </c>
       <c r="G70">
         <v>19.7</v>
@@ -7027,37 +7027,37 @@
         <v>7.205</v>
       </c>
       <c r="M70">
-        <v>19.1931768</v>
+        <v>19.4754294</v>
       </c>
       <c r="N70">
-        <v>-11.9881768</v>
+        <v>-12.2704294</v>
       </c>
       <c r="O70">
-        <v>-2.9970442</v>
+        <v>-3.067607350000001</v>
       </c>
       <c r="P70">
-        <v>-8.9911326</v>
+        <v>-9.202822050000002</v>
       </c>
       <c r="Q70">
-        <v>-5.5711326</v>
+        <v>-5.782822050000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2206673142618707</v>
+        <v>0.2263081953670923</v>
       </c>
       <c r="T70">
-        <v>1.691100576922069</v>
+        <v>1.745652208435684</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09384845556156186</v>
+        <v>0.09248833301719138</v>
       </c>
       <c r="W70">
-        <v>0.2136705341785837</v>
+        <v>0.2139912510745463</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3753938222462474</v>
+        <v>0.3699533320687656</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2178095038052356</v>
+        <v>0.2197095038052356</v>
       </c>
       <c r="C71">
-        <v>-26.58848675600417</v>
+        <v>-28.1821216359521</v>
       </c>
       <c r="D71">
-        <v>36.30451324399584</v>
+        <v>35.90787836404791</v>
       </c>
       <c r="E71">
-        <v>59.993</v>
+        <v>61.19</v>
       </c>
       <c r="F71">
-        <v>82.593</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="G71">
         <v>19.7</v>
@@ -7109,37 +7109,37 @@
         <v>7.205</v>
       </c>
       <c r="M71">
-        <v>19.4754294</v>
+        <v>19.757682</v>
       </c>
       <c r="N71">
-        <v>-12.2704294</v>
+        <v>-12.552682</v>
       </c>
       <c r="O71">
-        <v>-3.067607350000001</v>
+        <v>-3.138170500000001</v>
       </c>
       <c r="P71">
-        <v>-9.202822050000002</v>
+        <v>-9.414511500000001</v>
       </c>
       <c r="Q71">
-        <v>-5.782822050000002</v>
+        <v>-5.994511500000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2263081953670923</v>
+        <v>0.2323251352126621</v>
       </c>
       <c r="T71">
-        <v>1.745652208435684</v>
+        <v>1.80384061538354</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09248833301719138</v>
+        <v>0.09116707111694579</v>
       </c>
       <c r="W71">
-        <v>0.2139912510745463</v>
+        <v>0.2143028046306242</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3699533320687656</v>
+        <v>0.3646682844677832</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2197095038052356</v>
+        <v>0.2216095038052355</v>
       </c>
       <c r="C72">
-        <v>-28.1821216359521</v>
+        <v>-29.76718352916618</v>
       </c>
       <c r="D72">
-        <v>35.90787836404791</v>
+        <v>35.51981647083382</v>
       </c>
       <c r="E72">
-        <v>61.19</v>
+        <v>62.38699999999999</v>
       </c>
       <c r="F72">
-        <v>83.79000000000001</v>
+        <v>84.98699999999999</v>
       </c>
       <c r="G72">
         <v>19.7</v>
@@ -7191,37 +7191,37 @@
         <v>7.205</v>
       </c>
       <c r="M72">
-        <v>19.757682</v>
+        <v>20.0399346</v>
       </c>
       <c r="N72">
-        <v>-12.552682</v>
+        <v>-12.8349346</v>
       </c>
       <c r="O72">
-        <v>-3.138170500000001</v>
+        <v>-3.20873365</v>
       </c>
       <c r="P72">
-        <v>-9.414511500000001</v>
+        <v>-9.626200949999999</v>
       </c>
       <c r="Q72">
-        <v>-5.994511500000002</v>
+        <v>-6.206200949999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2323251352126621</v>
+        <v>0.2387570364268918</v>
       </c>
       <c r="T72">
-        <v>1.80384061538354</v>
+        <v>1.866042015914007</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09116707111694579</v>
+        <v>0.08988302786177756</v>
       </c>
       <c r="W72">
-        <v>0.2143028046306242</v>
+        <v>0.2146055820301928</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3646682844677832</v>
+        <v>0.3595321114471103</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2216095038052355</v>
+        <v>0.2235095038052355</v>
       </c>
       <c r="C73">
-        <v>-29.76718352916618</v>
+        <v>-31.34394741263607</v>
       </c>
       <c r="D73">
-        <v>35.51981647083382</v>
+        <v>35.14005258736392</v>
       </c>
       <c r="E73">
-        <v>62.38699999999999</v>
+        <v>63.58399999999998</v>
       </c>
       <c r="F73">
-        <v>84.98699999999999</v>
+        <v>86.18399999999998</v>
       </c>
       <c r="G73">
         <v>19.7</v>
@@ -7273,37 +7273,37 @@
         <v>7.205</v>
       </c>
       <c r="M73">
-        <v>20.0399346</v>
+        <v>20.3221872</v>
       </c>
       <c r="N73">
-        <v>-12.8349346</v>
+        <v>-13.1171872</v>
       </c>
       <c r="O73">
-        <v>-3.20873365</v>
+        <v>-3.2792968</v>
       </c>
       <c r="P73">
-        <v>-9.626200949999999</v>
+        <v>-9.837890399999999</v>
       </c>
       <c r="Q73">
-        <v>-6.206200949999999</v>
+        <v>-6.417890399999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2387570364268917</v>
+        <v>0.2456483591564236</v>
       </c>
       <c r="T73">
-        <v>1.866042015914006</v>
+        <v>1.932686373625221</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08988302786177756</v>
+        <v>0.08863465247480842</v>
       </c>
       <c r="W73">
-        <v>0.2146055820301928</v>
+        <v>0.2148999489464402</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3595321114471103</v>
+        <v>0.3545386098992337</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2235095038052355</v>
+        <v>0.2254095038052355</v>
       </c>
       <c r="C74">
-        <v>-31.34394741263607</v>
+        <v>-32.91267662796974</v>
       </c>
       <c r="D74">
-        <v>35.14005258736392</v>
+        <v>34.76832337203025</v>
       </c>
       <c r="E74">
-        <v>63.58399999999998</v>
+        <v>64.78099999999998</v>
       </c>
       <c r="F74">
-        <v>86.18399999999998</v>
+        <v>87.38099999999999</v>
       </c>
       <c r="G74">
         <v>19.7</v>
@@ -7355,37 +7355,37 @@
         <v>7.205</v>
       </c>
       <c r="M74">
-        <v>20.3221872</v>
+        <v>20.6044398</v>
       </c>
       <c r="N74">
-        <v>-13.1171872</v>
+        <v>-13.3994398</v>
       </c>
       <c r="O74">
-        <v>-3.2792968</v>
+        <v>-3.349859949999999</v>
       </c>
       <c r="P74">
-        <v>-9.837890399999999</v>
+        <v>-10.04957985</v>
       </c>
       <c r="Q74">
-        <v>-6.417890399999999</v>
+        <v>-6.629579849999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2456483591564236</v>
+        <v>0.2530501502362911</v>
       </c>
       <c r="T74">
-        <v>1.932686373625221</v>
+        <v>2.004267350426155</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08863465247480842</v>
+        <v>0.08742047915323571</v>
       </c>
       <c r="W74">
-        <v>0.2148999489464402</v>
+        <v>0.215186251015667</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3545386098992337</v>
+        <v>0.3496819166129429</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2254095038052355</v>
+        <v>0.2273095038052355</v>
       </c>
       <c r="C75">
-        <v>-32.91267662796974</v>
+        <v>-34.47362349037614</v>
       </c>
       <c r="D75">
-        <v>34.76832337203025</v>
+        <v>34.40437650962385</v>
       </c>
       <c r="E75">
-        <v>64.78099999999998</v>
+        <v>65.97799999999998</v>
       </c>
       <c r="F75">
-        <v>87.38099999999999</v>
+        <v>88.57799999999999</v>
       </c>
       <c r="G75">
         <v>19.7</v>
@@ -7437,37 +7437,37 @@
         <v>7.205</v>
       </c>
       <c r="M75">
-        <v>20.6044398</v>
+        <v>20.8866924</v>
       </c>
       <c r="N75">
-        <v>-13.3994398</v>
+        <v>-13.6816924</v>
       </c>
       <c r="O75">
-        <v>-3.349859949999999</v>
+        <v>-3.420423099999999</v>
       </c>
       <c r="P75">
-        <v>-10.04957985</v>
+        <v>-10.2612693</v>
       </c>
       <c r="Q75">
-        <v>-6.629579849999999</v>
+        <v>-6.841269299999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2530501502362911</v>
+        <v>0.2610213098607639</v>
       </c>
       <c r="T75">
-        <v>2.004267350426155</v>
+        <v>2.081354556211776</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08742047915323571</v>
+        <v>0.08623912132684064</v>
       </c>
       <c r="W75">
-        <v>0.215186251015667</v>
+        <v>0.215464815191131</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3496819166129429</v>
+        <v>0.3449564853073626</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2273095038052355</v>
+        <v>0.2292095038052356</v>
       </c>
       <c r="C76">
-        <v>-34.47362349037614</v>
+        <v>-36.0270298597958</v>
       </c>
       <c r="D76">
-        <v>34.40437650962385</v>
+        <v>34.04797014020419</v>
       </c>
       <c r="E76">
-        <v>65.97799999999998</v>
+        <v>67.17499999999998</v>
       </c>
       <c r="F76">
-        <v>88.57799999999999</v>
+        <v>89.77499999999999</v>
       </c>
       <c r="G76">
         <v>19.7</v>
@@ -7519,37 +7519,37 @@
         <v>7.205</v>
       </c>
       <c r="M76">
-        <v>20.8866924</v>
+        <v>21.168945</v>
       </c>
       <c r="N76">
-        <v>-13.6816924</v>
+        <v>-13.963945</v>
       </c>
       <c r="O76">
-        <v>-3.420423099999999</v>
+        <v>-3.490986249999999</v>
       </c>
       <c r="P76">
-        <v>-10.2612693</v>
+        <v>-10.47295875</v>
       </c>
       <c r="Q76">
-        <v>-6.841269299999999</v>
+        <v>-7.052958749999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2610213098607639</v>
+        <v>0.2696301622551945</v>
       </c>
       <c r="T76">
-        <v>2.081354556211776</v>
+        <v>2.164608738460248</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08623912132684064</v>
+        <v>0.0850892663758161</v>
       </c>
       <c r="W76">
-        <v>0.215464815191131</v>
+        <v>0.2157359509885826</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3449564853073626</v>
+        <v>0.3403570655032644</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2292095038052356</v>
+        <v>0.2311095038052355</v>
       </c>
       <c r="C77">
-        <v>-36.0270298597958</v>
+        <v>-37.57312767689632</v>
       </c>
       <c r="D77">
-        <v>34.04797014020419</v>
+        <v>33.69887232310367</v>
       </c>
       <c r="E77">
-        <v>67.17499999999998</v>
+        <v>68.37199999999999</v>
       </c>
       <c r="F77">
-        <v>89.77499999999999</v>
+        <v>90.97199999999999</v>
       </c>
       <c r="G77">
         <v>19.7</v>
@@ -7601,37 +7601,37 @@
         <v>7.205</v>
       </c>
       <c r="M77">
-        <v>21.168945</v>
+        <v>21.4511976</v>
       </c>
       <c r="N77">
-        <v>-13.963945</v>
+        <v>-14.2461976</v>
       </c>
       <c r="O77">
-        <v>-3.490986249999999</v>
+        <v>-3.5615494</v>
       </c>
       <c r="P77">
-        <v>-10.47295875</v>
+        <v>-10.6846482</v>
       </c>
       <c r="Q77">
-        <v>-7.052958749999998</v>
+        <v>-7.2646482</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2696301622551945</v>
+        <v>0.2789564190158276</v>
       </c>
       <c r="T77">
-        <v>2.164608738460248</v>
+        <v>2.254800769229425</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0850892663758161</v>
+        <v>0.08396967076560798</v>
       </c>
       <c r="W77">
-        <v>0.2157359509885826</v>
+        <v>0.2159999516334696</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3403570655032644</v>
+        <v>0.335878683062432</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2311095038052355</v>
+        <v>0.2330095038052356</v>
       </c>
       <c r="C78">
-        <v>-37.57312767689632</v>
+        <v>-39.1121394664287</v>
       </c>
       <c r="D78">
-        <v>33.69887232310367</v>
+        <v>33.35686053357129</v>
       </c>
       <c r="E78">
-        <v>68.37199999999999</v>
+        <v>69.56899999999999</v>
       </c>
       <c r="F78">
-        <v>90.97199999999999</v>
+        <v>92.169</v>
       </c>
       <c r="G78">
         <v>19.7</v>
@@ -7683,37 +7683,37 @@
         <v>7.205</v>
       </c>
       <c r="M78">
-        <v>21.4511976</v>
+        <v>21.7334502</v>
       </c>
       <c r="N78">
-        <v>-14.2461976</v>
+        <v>-14.5284502</v>
       </c>
       <c r="O78">
-        <v>-3.5615494</v>
+        <v>-3.63211255</v>
       </c>
       <c r="P78">
-        <v>-10.6846482</v>
+        <v>-10.89633765</v>
       </c>
       <c r="Q78">
-        <v>-7.2646482</v>
+        <v>-7.47633765</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2789564190158276</v>
+        <v>0.2890936546252114</v>
       </c>
       <c r="T78">
-        <v>2.254800769229425</v>
+        <v>2.352835585282878</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08396967076560798</v>
+        <v>0.08287915556085983</v>
       </c>
       <c r="W78">
-        <v>0.2159999516334696</v>
+        <v>0.2162570951187493</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.335878683062432</v>
+        <v>0.3315166222434393</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2330095038052356</v>
+        <v>0.2349095038052356</v>
       </c>
       <c r="C79">
-        <v>-39.1121394664287</v>
+        <v>-40.64427881024011</v>
       </c>
       <c r="D79">
-        <v>33.35686053357129</v>
+        <v>33.02172118975989</v>
       </c>
       <c r="E79">
-        <v>69.56899999999999</v>
+        <v>70.76599999999999</v>
       </c>
       <c r="F79">
-        <v>92.169</v>
+        <v>93.366</v>
       </c>
       <c r="G79">
         <v>19.7</v>
@@ -7765,37 +7765,37 @@
         <v>7.205</v>
       </c>
       <c r="M79">
-        <v>21.7334502</v>
+        <v>22.0157028</v>
       </c>
       <c r="N79">
-        <v>-14.5284502</v>
+        <v>-14.8107028</v>
       </c>
       <c r="O79">
-        <v>-3.63211255</v>
+        <v>-3.7026757</v>
       </c>
       <c r="P79">
-        <v>-10.89633765</v>
+        <v>-11.1080271</v>
       </c>
       <c r="Q79">
-        <v>-7.47633765</v>
+        <v>-7.688027099999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2890936546252114</v>
+        <v>0.3001524571081755</v>
       </c>
       <c r="T79">
-        <v>2.352835585282878</v>
+        <v>2.459782657341191</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08287915556085983</v>
+        <v>0.08181660228443854</v>
       </c>
       <c r="W79">
-        <v>0.2162570951187493</v>
+        <v>0.2165076451813294</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3315166222434393</v>
+        <v>0.3272664091377542</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2349095038052356</v>
+        <v>0.2368095038052355</v>
       </c>
       <c r="C80">
-        <v>-40.64427881024011</v>
+        <v>-42.16975079205582</v>
       </c>
       <c r="D80">
-        <v>33.02172118975989</v>
+        <v>32.69324920794417</v>
       </c>
       <c r="E80">
-        <v>70.76599999999999</v>
+        <v>71.96299999999999</v>
       </c>
       <c r="F80">
-        <v>93.366</v>
+        <v>94.56299999999999</v>
       </c>
       <c r="G80">
         <v>19.7</v>
@@ -7847,37 +7847,37 @@
         <v>7.205</v>
       </c>
       <c r="M80">
-        <v>22.0157028</v>
+        <v>22.2979554</v>
       </c>
       <c r="N80">
-        <v>-14.8107028</v>
+        <v>-15.0929554</v>
       </c>
       <c r="O80">
-        <v>-3.7026757</v>
+        <v>-3.77323885</v>
       </c>
       <c r="P80">
-        <v>-11.1080271</v>
+        <v>-11.31971655</v>
       </c>
       <c r="Q80">
-        <v>-7.688027099999999</v>
+        <v>-7.899716549999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3001524571081755</v>
+        <v>0.3122644788752316</v>
       </c>
       <c r="T80">
-        <v>2.459782657341191</v>
+        <v>2.576915164833629</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08181660228443854</v>
+        <v>0.08078094909096464</v>
       </c>
       <c r="W80">
-        <v>0.2165076451813294</v>
+        <v>0.2167518522043505</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3272664091377542</v>
+        <v>0.3231237963638586</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2368095038052355</v>
+        <v>0.2387095038052355</v>
       </c>
       <c r="C81">
-        <v>-42.16975079205582</v>
+        <v>-43.68875241597689</v>
       </c>
       <c r="D81">
-        <v>32.69324920794417</v>
+        <v>32.3712475840231</v>
       </c>
       <c r="E81">
-        <v>71.96299999999999</v>
+        <v>73.16</v>
       </c>
       <c r="F81">
-        <v>94.56299999999999</v>
+        <v>95.75999999999999</v>
       </c>
       <c r="G81">
         <v>19.7</v>
@@ -7929,37 +7929,37 @@
         <v>7.205</v>
       </c>
       <c r="M81">
-        <v>22.2979554</v>
+        <v>22.580208</v>
       </c>
       <c r="N81">
-        <v>-15.0929554</v>
+        <v>-15.375208</v>
       </c>
       <c r="O81">
-        <v>-3.77323885</v>
+        <v>-3.843802</v>
       </c>
       <c r="P81">
-        <v>-11.31971655</v>
+        <v>-11.531406</v>
       </c>
       <c r="Q81">
-        <v>-7.899716549999999</v>
+        <v>-8.111405999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3122644788752316</v>
+        <v>0.3255877028189931</v>
       </c>
       <c r="T81">
-        <v>2.576915164833629</v>
+        <v>2.70576092307531</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08078094909096464</v>
+        <v>0.07977118722732758</v>
       </c>
       <c r="W81">
-        <v>0.2167518522043505</v>
+        <v>0.2169899540517962</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3231237963638586</v>
+        <v>0.3190847489093104</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2387095038052355</v>
+        <v>0.2406095038052355</v>
       </c>
       <c r="C82">
-        <v>-43.68875241597689</v>
+        <v>-45.20147300048768</v>
       </c>
       <c r="D82">
-        <v>32.3712475840231</v>
+        <v>32.05552699951232</v>
       </c>
       <c r="E82">
-        <v>73.16</v>
+        <v>74.357</v>
       </c>
       <c r="F82">
-        <v>95.75999999999999</v>
+        <v>96.95699999999999</v>
       </c>
       <c r="G82">
         <v>19.7</v>
@@ -8011,37 +8011,37 @@
         <v>7.205</v>
       </c>
       <c r="M82">
-        <v>22.580208</v>
+        <v>22.8624606</v>
       </c>
       <c r="N82">
-        <v>-15.375208</v>
+        <v>-15.6574606</v>
       </c>
       <c r="O82">
-        <v>-3.843802</v>
+        <v>-3.91436515</v>
       </c>
       <c r="P82">
-        <v>-11.531406</v>
+        <v>-11.74309545</v>
       </c>
       <c r="Q82">
-        <v>-8.111405999999999</v>
+        <v>-8.323095449999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3255877028189931</v>
+        <v>0.3403133713884138</v>
       </c>
       <c r="T82">
-        <v>2.70576092307531</v>
+        <v>2.848169392710853</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07977118722732758</v>
+        <v>0.07878635775538527</v>
       </c>
       <c r="W82">
-        <v>0.2169899540517962</v>
+        <v>0.2172221768412802</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3190847489093104</v>
+        <v>0.315145431021541</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2406095038052355</v>
+        <v>0.2425095038052356</v>
       </c>
       <c r="C83">
-        <v>-45.20147300048768</v>
+        <v>-46.70809454962939</v>
       </c>
       <c r="D83">
-        <v>32.05552699951232</v>
+        <v>31.74590545037061</v>
       </c>
       <c r="E83">
-        <v>74.357</v>
+        <v>75.554</v>
       </c>
       <c r="F83">
-        <v>96.95699999999999</v>
+        <v>98.154</v>
       </c>
       <c r="G83">
         <v>19.7</v>
@@ -8093,37 +8093,37 @@
         <v>7.205</v>
       </c>
       <c r="M83">
-        <v>22.8624606</v>
+        <v>23.1447132</v>
       </c>
       <c r="N83">
-        <v>-15.6574606</v>
+        <v>-15.9397132</v>
       </c>
       <c r="O83">
-        <v>-3.91436515</v>
+        <v>-3.9849283</v>
       </c>
       <c r="P83">
-        <v>-11.74309545</v>
+        <v>-11.9547849</v>
       </c>
       <c r="Q83">
-        <v>-8.323095449999999</v>
+        <v>-8.534784900000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3403133713884138</v>
+        <v>0.3566752253544369</v>
       </c>
       <c r="T83">
-        <v>2.848169392710853</v>
+        <v>3.006401025639234</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07878635775538527</v>
+        <v>0.07782554851446592</v>
       </c>
       <c r="W83">
-        <v>0.2172221768412802</v>
+        <v>0.217448735660289</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.315145431021541</v>
+        <v>0.3113021940578637</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2425095038052356</v>
+        <v>0.2444095038052355</v>
       </c>
       <c r="C84">
-        <v>-46.70809454962939</v>
+        <v>-48.20879210286859</v>
       </c>
       <c r="D84">
-        <v>31.74590545037061</v>
+        <v>31.44220789713141</v>
       </c>
       <c r="E84">
-        <v>75.554</v>
+        <v>76.751</v>
       </c>
       <c r="F84">
-        <v>98.154</v>
+        <v>99.351</v>
       </c>
       <c r="G84">
         <v>19.7</v>
@@ -8175,37 +8175,37 @@
         <v>7.205</v>
       </c>
       <c r="M84">
-        <v>23.1447132</v>
+        <v>23.4269658</v>
       </c>
       <c r="N84">
-        <v>-15.9397132</v>
+        <v>-16.2219658</v>
       </c>
       <c r="O84">
-        <v>-3.9849283</v>
+        <v>-4.05549145</v>
       </c>
       <c r="P84">
-        <v>-11.9547849</v>
+        <v>-12.16647435</v>
       </c>
       <c r="Q84">
-        <v>-8.534784900000002</v>
+        <v>-8.74647435</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3566752253544369</v>
+        <v>0.3749620033164626</v>
       </c>
       <c r="T84">
-        <v>3.006401025639234</v>
+        <v>3.183248144794483</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07782554851446592</v>
+        <v>0.07688789130344827</v>
       </c>
       <c r="W84">
-        <v>0.217448735660289</v>
+        <v>0.2176698352306469</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3113021940578637</v>
+        <v>0.3075515652137931</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2444095038052355</v>
+        <v>0.2463095038052356</v>
       </c>
       <c r="C85">
-        <v>-48.20879210286859</v>
+        <v>-49.70373406507393</v>
       </c>
       <c r="D85">
-        <v>31.44220789713141</v>
+        <v>31.14426593492607</v>
       </c>
       <c r="E85">
-        <v>76.751</v>
+        <v>77.94800000000001</v>
       </c>
       <c r="F85">
-        <v>99.351</v>
+        <v>100.548</v>
       </c>
       <c r="G85">
         <v>19.7</v>
@@ -8257,37 +8257,37 @@
         <v>7.205</v>
       </c>
       <c r="M85">
-        <v>23.4269658</v>
+        <v>23.7092184</v>
       </c>
       <c r="N85">
-        <v>-16.2219658</v>
+        <v>-16.5042184</v>
       </c>
       <c r="O85">
-        <v>-4.05549145</v>
+        <v>-4.1260546</v>
       </c>
       <c r="P85">
-        <v>-12.16647435</v>
+        <v>-12.3781638</v>
       </c>
       <c r="Q85">
-        <v>-8.74647435</v>
+        <v>-8.958163799999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3749620033164626</v>
+        <v>0.3955346285237415</v>
       </c>
       <c r="T85">
-        <v>3.183248144794483</v>
+        <v>3.382201153844139</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07688789130344827</v>
+        <v>0.0759725592641215</v>
       </c>
       <c r="W85">
-        <v>0.2176698352306469</v>
+        <v>0.2178856705255202</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3075515652137931</v>
+        <v>0.3038902370564861</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2463095038052356</v>
+        <v>0.2482095038052356</v>
       </c>
       <c r="C86">
-        <v>-49.70373406507392</v>
+        <v>-51.19308251790792</v>
       </c>
       <c r="D86">
-        <v>31.14426593492607</v>
+        <v>30.85191748209207</v>
       </c>
       <c r="E86">
-        <v>77.94799999999998</v>
+        <v>79.14499999999998</v>
       </c>
       <c r="F86">
-        <v>100.548</v>
+        <v>101.745</v>
       </c>
       <c r="G86">
         <v>19.7</v>
@@ -8339,37 +8339,37 @@
         <v>7.205</v>
       </c>
       <c r="M86">
-        <v>23.7092184</v>
+        <v>23.991471</v>
       </c>
       <c r="N86">
-        <v>-16.5042184</v>
+        <v>-16.786471</v>
       </c>
       <c r="O86">
-        <v>-4.1260546</v>
+        <v>-4.19661775</v>
       </c>
       <c r="P86">
-        <v>-12.3781638</v>
+        <v>-12.58985325</v>
       </c>
       <c r="Q86">
-        <v>-8.958163799999999</v>
+        <v>-9.169853249999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3955346285237413</v>
+        <v>0.4188502704253241</v>
       </c>
       <c r="T86">
-        <v>3.382201153844136</v>
+        <v>3.60768123076708</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07597255926412151</v>
+        <v>0.07507876444924949</v>
       </c>
       <c r="W86">
-        <v>0.2178856705255202</v>
+        <v>0.218096427342867</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.303890237056486</v>
+        <v>0.3003150577969979</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2482095038052356</v>
+        <v>0.2501095038052356</v>
       </c>
       <c r="C87">
-        <v>-51.19308251790792</v>
+        <v>-52.67699351384407</v>
       </c>
       <c r="D87">
-        <v>30.85191748209207</v>
+        <v>30.56500648615593</v>
       </c>
       <c r="E87">
-        <v>79.14499999999998</v>
+        <v>80.34199999999998</v>
       </c>
       <c r="F87">
-        <v>101.745</v>
+        <v>102.942</v>
       </c>
       <c r="G87">
         <v>19.7</v>
@@ -8421,37 +8421,37 @@
         <v>7.205</v>
       </c>
       <c r="M87">
-        <v>23.991471</v>
+        <v>24.2737236</v>
       </c>
       <c r="N87">
-        <v>-16.786471</v>
+        <v>-17.0687236</v>
       </c>
       <c r="O87">
-        <v>-4.19661775</v>
+        <v>-4.2671809</v>
       </c>
       <c r="P87">
-        <v>-12.58985325</v>
+        <v>-12.8015427</v>
       </c>
       <c r="Q87">
-        <v>-9.169853249999999</v>
+        <v>-9.381542699999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4188502704253241</v>
+        <v>0.4454967183128472</v>
       </c>
       <c r="T87">
-        <v>3.60768123076708</v>
+        <v>3.865372747250442</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07507876444924949</v>
+        <v>0.07420575556030472</v>
       </c>
       <c r="W87">
-        <v>0.218096427342867</v>
+        <v>0.2183022828388801</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3003150577969979</v>
+        <v>0.2968230222412189</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2501095038052356</v>
+        <v>0.2520095038052356</v>
       </c>
       <c r="C88">
-        <v>-52.67699351384407</v>
+        <v>-54.15561735392928</v>
       </c>
       <c r="D88">
-        <v>30.56500648615593</v>
+        <v>30.28338264607072</v>
       </c>
       <c r="E88">
-        <v>80.34199999999998</v>
+        <v>81.53899999999999</v>
       </c>
       <c r="F88">
-        <v>102.942</v>
+        <v>104.139</v>
       </c>
       <c r="G88">
         <v>19.7</v>
@@ -8503,37 +8503,37 @@
         <v>7.205</v>
       </c>
       <c r="M88">
-        <v>24.2737236</v>
+        <v>24.5559762</v>
       </c>
       <c r="N88">
-        <v>-17.0687236</v>
+        <v>-17.3509762</v>
       </c>
       <c r="O88">
-        <v>-4.2671809</v>
+        <v>-4.33774405</v>
       </c>
       <c r="P88">
-        <v>-12.8015427</v>
+        <v>-13.01323215</v>
       </c>
       <c r="Q88">
-        <v>-9.381542699999999</v>
+        <v>-9.593232149999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4454967183128472</v>
+        <v>0.4762426197215278</v>
       </c>
       <c r="T88">
-        <v>3.865372747250442</v>
+        <v>4.162709112423553</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07420575556030472</v>
+        <v>0.07335281584122076</v>
       </c>
       <c r="W88">
-        <v>0.2183022828388801</v>
+        <v>0.2185034060246402</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2968230222412189</v>
+        <v>0.2934112633648831</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2520095038052356</v>
+        <v>0.2539095038052356</v>
       </c>
       <c r="C89">
-        <v>-54.15561735392928</v>
+        <v>-55.62909885033119</v>
       </c>
       <c r="D89">
-        <v>30.28338264607072</v>
+        <v>30.00690114966879</v>
       </c>
       <c r="E89">
-        <v>81.53899999999999</v>
+        <v>82.73599999999999</v>
       </c>
       <c r="F89">
-        <v>104.139</v>
+        <v>105.336</v>
       </c>
       <c r="G89">
         <v>19.7</v>
@@ -8585,37 +8585,37 @@
         <v>7.205</v>
       </c>
       <c r="M89">
-        <v>24.5559762</v>
+        <v>24.8382288</v>
       </c>
       <c r="N89">
-        <v>-17.3509762</v>
+        <v>-17.6332288</v>
       </c>
       <c r="O89">
-        <v>-4.33774405</v>
+        <v>-4.408307199999999</v>
       </c>
       <c r="P89">
-        <v>-13.01323215</v>
+        <v>-13.2249216</v>
       </c>
       <c r="Q89">
-        <v>-9.593232149999999</v>
+        <v>-9.804921599999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4762426197215278</v>
+        <v>0.5121128380316552</v>
       </c>
       <c r="T89">
-        <v>4.162709112423553</v>
+        <v>4.50960153845885</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07335281584122076</v>
+        <v>0.07251926111575235</v>
       </c>
       <c r="W89">
-        <v>0.2185034060246402</v>
+        <v>0.2186999582289056</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2934112633648831</v>
+        <v>0.2900770444630093</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2539095038052356</v>
+        <v>0.2558095038052355</v>
       </c>
       <c r="C90">
-        <v>-55.62909885033119</v>
+        <v>-57.09757757463333</v>
       </c>
       <c r="D90">
-        <v>30.00690114966879</v>
+        <v>29.73542242536666</v>
       </c>
       <c r="E90">
-        <v>82.73599999999999</v>
+        <v>83.93299999999999</v>
       </c>
       <c r="F90">
-        <v>105.336</v>
+        <v>106.533</v>
       </c>
       <c r="G90">
         <v>19.7</v>
@@ -8667,37 +8667,37 @@
         <v>7.205</v>
       </c>
       <c r="M90">
-        <v>24.8382288</v>
+        <v>25.1204814</v>
       </c>
       <c r="N90">
-        <v>-17.6332288</v>
+        <v>-17.9154814</v>
       </c>
       <c r="O90">
-        <v>-4.408307199999999</v>
+        <v>-4.478870349999999</v>
       </c>
       <c r="P90">
-        <v>-13.2249216</v>
+        <v>-13.43661105</v>
       </c>
       <c r="Q90">
-        <v>-9.804921599999998</v>
+        <v>-10.01661105</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5121128380316552</v>
+        <v>0.554504914216351</v>
       </c>
       <c r="T90">
-        <v>4.50960153845885</v>
+        <v>4.919565314682381</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07251926111575235</v>
+        <v>0.07170443795714838</v>
       </c>
       <c r="W90">
-        <v>0.2186999582289056</v>
+        <v>0.2188920935297044</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2900770444630093</v>
+        <v>0.2868177518285936</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2558095038052355</v>
+        <v>0.2577095038052355</v>
       </c>
       <c r="C91">
-        <v>-57.09757757463333</v>
+        <v>-58.56118809277282</v>
       </c>
       <c r="D91">
-        <v>29.73542242536666</v>
+        <v>29.46881190722717</v>
       </c>
       <c r="E91">
-        <v>83.93299999999999</v>
+        <v>85.13</v>
       </c>
       <c r="F91">
-        <v>106.533</v>
+        <v>107.73</v>
       </c>
       <c r="G91">
         <v>19.7</v>
@@ -8749,37 +8749,37 @@
         <v>7.205</v>
       </c>
       <c r="M91">
-        <v>25.1204814</v>
+        <v>25.402734</v>
       </c>
       <c r="N91">
-        <v>-17.9154814</v>
+        <v>-18.197734</v>
       </c>
       <c r="O91">
-        <v>-4.478870349999999</v>
+        <v>-4.549433499999999</v>
       </c>
       <c r="P91">
-        <v>-13.43661105</v>
+        <v>-13.6483005</v>
       </c>
       <c r="Q91">
-        <v>-10.01661105</v>
+        <v>-10.2283005</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.554504914216351</v>
+        <v>0.6053754056379861</v>
       </c>
       <c r="T91">
-        <v>4.919565314682381</v>
+        <v>5.411521846150619</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07170443795714838</v>
+        <v>0.07090772197984674</v>
       </c>
       <c r="W91">
-        <v>0.2188920935297044</v>
+        <v>0.2190799591571521</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2868177518285936</v>
+        <v>0.2836308879193871</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2577095038052355</v>
+        <v>0.2596095038052356</v>
       </c>
       <c r="C92">
-        <v>-58.56118809277282</v>
+        <v>-60.02006018745173</v>
       </c>
       <c r="D92">
-        <v>29.46881190722717</v>
+        <v>29.20693981254827</v>
       </c>
       <c r="E92">
-        <v>85.13</v>
+        <v>86.327</v>
       </c>
       <c r="F92">
-        <v>107.73</v>
+        <v>108.927</v>
       </c>
       <c r="G92">
         <v>19.7</v>
@@ -8831,37 +8831,37 @@
         <v>7.205</v>
       </c>
       <c r="M92">
-        <v>25.402734</v>
+        <v>25.6849866</v>
       </c>
       <c r="N92">
-        <v>-18.197734</v>
+        <v>-18.4799866</v>
       </c>
       <c r="O92">
-        <v>-4.549433499999999</v>
+        <v>-4.619996649999999</v>
       </c>
       <c r="P92">
-        <v>-13.6483005</v>
+        <v>-13.85998995</v>
       </c>
       <c r="Q92">
-        <v>-10.2283005</v>
+        <v>-10.43998995</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6053754056379861</v>
+        <v>0.6675504507088736</v>
       </c>
       <c r="T92">
-        <v>5.411521846150619</v>
+        <v>6.012802051278467</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07090772197984674</v>
+        <v>0.07012851624380446</v>
       </c>
       <c r="W92">
-        <v>0.2190799591571521</v>
+        <v>0.2192636958697109</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2836308879193871</v>
+        <v>0.2805140649752179</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2596095038052356</v>
+        <v>0.2615095038052355</v>
       </c>
       <c r="C93">
-        <v>-60.02006018745173</v>
+        <v>-61.47431906879405</v>
       </c>
       <c r="D93">
-        <v>29.20693981254827</v>
+        <v>28.94968093120595</v>
       </c>
       <c r="E93">
-        <v>86.327</v>
+        <v>87.524</v>
       </c>
       <c r="F93">
-        <v>108.927</v>
+        <v>110.124</v>
       </c>
       <c r="G93">
         <v>19.7</v>
@@ -8913,37 +8913,37 @@
         <v>7.205</v>
       </c>
       <c r="M93">
-        <v>25.6849866</v>
+        <v>25.9672392</v>
       </c>
       <c r="N93">
-        <v>-18.4799866</v>
+        <v>-18.7622392</v>
       </c>
       <c r="O93">
-        <v>-4.619996649999999</v>
+        <v>-4.690559800000001</v>
       </c>
       <c r="P93">
-        <v>-13.85998995</v>
+        <v>-14.0716794</v>
       </c>
       <c r="Q93">
-        <v>-10.43998995</v>
+        <v>-10.6516794</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6675504507088736</v>
+        <v>0.745269257047483</v>
       </c>
       <c r="T93">
-        <v>6.012802051278467</v>
+        <v>6.764402307688278</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07012851624380446</v>
+        <v>0.06936624976289354</v>
       </c>
       <c r="W93">
-        <v>0.2192636958697109</v>
+        <v>0.2194434383059097</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2805140649752179</v>
+        <v>0.2774649990515741</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2615095038052355</v>
+        <v>0.2634095038052356</v>
       </c>
       <c r="C94">
-        <v>-61.47431906879405</v>
+        <v>-62.9240855739671</v>
       </c>
       <c r="D94">
-        <v>28.94968093120595</v>
+        <v>28.69691442603289</v>
       </c>
       <c r="E94">
-        <v>87.524</v>
+        <v>88.721</v>
       </c>
       <c r="F94">
-        <v>110.124</v>
+        <v>111.321</v>
       </c>
       <c r="G94">
         <v>19.7</v>
@@ -8995,37 +8995,37 @@
         <v>7.205</v>
       </c>
       <c r="M94">
-        <v>25.9672392</v>
+        <v>26.2494918</v>
       </c>
       <c r="N94">
-        <v>-18.7622392</v>
+        <v>-19.0444918</v>
       </c>
       <c r="O94">
-        <v>-4.690559800000001</v>
+        <v>-4.761122950000001</v>
       </c>
       <c r="P94">
-        <v>-14.0716794</v>
+        <v>-14.28336885</v>
       </c>
       <c r="Q94">
-        <v>-10.6516794</v>
+        <v>-10.86336885</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.745269257047483</v>
+        <v>0.845193436625695</v>
       </c>
       <c r="T94">
-        <v>6.764402307688278</v>
+        <v>7.73074549450089</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06936624976289354</v>
+        <v>0.06862037610952909</v>
       </c>
       <c r="W94">
-        <v>0.2194434383059097</v>
+        <v>0.2196193153133731</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2774649990515741</v>
+        <v>0.2744815044381164</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2634095038052356</v>
+        <v>0.2653095038052355</v>
       </c>
       <c r="C95">
-        <v>-62.9240855739671</v>
+        <v>-64.36947635643564</v>
       </c>
       <c r="D95">
-        <v>28.69691442603289</v>
+        <v>28.44852364356436</v>
       </c>
       <c r="E95">
-        <v>88.721</v>
+        <v>89.91800000000001</v>
       </c>
       <c r="F95">
-        <v>111.321</v>
+        <v>112.518</v>
       </c>
       <c r="G95">
         <v>19.7</v>
@@ -9077,37 +9077,37 @@
         <v>7.205</v>
       </c>
       <c r="M95">
-        <v>26.2494918</v>
+        <v>26.5317444</v>
       </c>
       <c r="N95">
-        <v>-19.0444918</v>
+        <v>-19.3267444</v>
       </c>
       <c r="O95">
-        <v>-4.761122950000001</v>
+        <v>-4.831686100000001</v>
       </c>
       <c r="P95">
-        <v>-14.28336885</v>
+        <v>-14.4950583</v>
       </c>
       <c r="Q95">
-        <v>-10.86336885</v>
+        <v>-11.0750583</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.845193436625695</v>
+        <v>0.978425676063311</v>
       </c>
       <c r="T95">
-        <v>7.73074549450089</v>
+        <v>9.019203076917707</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06862037610952909</v>
+        <v>0.06789037210836389</v>
       </c>
       <c r="W95">
-        <v>0.2196193153133731</v>
+        <v>0.2197914502568478</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2744815044381164</v>
+        <v>0.2715614884334555</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2653095038052355</v>
+        <v>0.2672095038052356</v>
       </c>
       <c r="C96">
-        <v>-64.36947635643564</v>
+        <v>-65.81060406547167</v>
       </c>
       <c r="D96">
-        <v>28.44852364356436</v>
+        <v>28.20439593452834</v>
       </c>
       <c r="E96">
-        <v>89.91800000000001</v>
+        <v>91.11500000000001</v>
       </c>
       <c r="F96">
-        <v>112.518</v>
+        <v>113.715</v>
       </c>
       <c r="G96">
         <v>19.7</v>
@@ -9159,37 +9159,37 @@
         <v>7.205</v>
       </c>
       <c r="M96">
-        <v>26.5317444</v>
+        <v>26.813997</v>
       </c>
       <c r="N96">
-        <v>-19.3267444</v>
+        <v>-19.608997</v>
       </c>
       <c r="O96">
-        <v>-4.831686100000001</v>
+        <v>-4.902249250000001</v>
       </c>
       <c r="P96">
-        <v>-14.4950583</v>
+        <v>-14.70674775</v>
       </c>
       <c r="Q96">
-        <v>-11.0750583</v>
+        <v>-11.28674775</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.978425676063311</v>
+        <v>1.164950811275974</v>
       </c>
       <c r="T96">
-        <v>9.019203076917707</v>
+        <v>10.82304369230125</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06789037210836389</v>
+        <v>0.06717573661248638</v>
       </c>
       <c r="W96">
-        <v>0.2197914502568478</v>
+        <v>0.2199599613067757</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2715614884334555</v>
+        <v>0.2687029464499454</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2672095038052356</v>
+        <v>0.2691095038052356</v>
       </c>
       <c r="C97">
-        <v>-65.81060406547167</v>
+        <v>-67.24757751650014</v>
       </c>
       <c r="D97">
-        <v>28.20439593452834</v>
+        <v>27.96442248349985</v>
       </c>
       <c r="E97">
-        <v>91.11500000000001</v>
+        <v>92.31199999999998</v>
       </c>
       <c r="F97">
-        <v>113.715</v>
+        <v>114.912</v>
       </c>
       <c r="G97">
         <v>19.7</v>
@@ -9241,37 +9241,37 @@
         <v>7.205</v>
       </c>
       <c r="M97">
-        <v>26.813997</v>
+        <v>27.0962496</v>
       </c>
       <c r="N97">
-        <v>-19.608997</v>
+        <v>-19.8912496</v>
       </c>
       <c r="O97">
-        <v>-4.902249250000001</v>
+        <v>-4.9728124</v>
       </c>
       <c r="P97">
-        <v>-14.70674775</v>
+        <v>-14.9184372</v>
       </c>
       <c r="Q97">
-        <v>-11.28674775</v>
+        <v>-11.4984372</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.164950811275974</v>
+        <v>1.444738514094968</v>
       </c>
       <c r="T97">
-        <v>10.82304369230125</v>
+        <v>13.52880461537657</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06717573661248638</v>
+        <v>0.06647598935610631</v>
       </c>
       <c r="W97">
-        <v>0.2199599613067757</v>
+        <v>0.2201249617098301</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2687029464499454</v>
+        <v>0.2659039574244252</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2691095038052356</v>
+        <v>0.2710095038052355</v>
       </c>
       <c r="C98">
-        <v>-67.24757751650014</v>
+        <v>-68.68050185282209</v>
       </c>
       <c r="D98">
-        <v>27.96442248349985</v>
+        <v>27.72849814717789</v>
       </c>
       <c r="E98">
-        <v>92.31199999999998</v>
+        <v>93.50899999999999</v>
       </c>
       <c r="F98">
-        <v>114.912</v>
+        <v>116.109</v>
       </c>
       <c r="G98">
         <v>19.7</v>
@@ -9323,37 +9323,37 @@
         <v>7.205</v>
       </c>
       <c r="M98">
-        <v>27.0962496</v>
+        <v>27.3785022</v>
       </c>
       <c r="N98">
-        <v>-19.8912496</v>
+        <v>-20.17350219999999</v>
       </c>
       <c r="O98">
-        <v>-4.9728124</v>
+        <v>-5.043375549999999</v>
       </c>
       <c r="P98">
-        <v>-14.9184372</v>
+        <v>-15.13012665</v>
       </c>
       <c r="Q98">
-        <v>-11.4984372</v>
+        <v>-11.71012665</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.444738514094964</v>
+        <v>1.911051352126619</v>
       </c>
       <c r="T98">
-        <v>13.52880461537654</v>
+        <v>18.03840615383538</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06647598935610631</v>
+        <v>0.06579066987820832</v>
       </c>
       <c r="W98">
-        <v>0.2201249617098301</v>
+        <v>0.2202865600427185</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2659039574244252</v>
+        <v>0.2631626795128333</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2710095038052355</v>
+        <v>0.2729095038052355</v>
       </c>
       <c r="C99">
-        <v>-68.68050185282209</v>
+        <v>-70.10947869921959</v>
       </c>
       <c r="D99">
-        <v>27.72849814717789</v>
+        <v>27.49652130078039</v>
       </c>
       <c r="E99">
-        <v>93.50899999999999</v>
+        <v>94.70599999999999</v>
       </c>
       <c r="F99">
-        <v>116.109</v>
+        <v>117.306</v>
       </c>
       <c r="G99">
         <v>19.7</v>
@@ -9405,37 +9405,37 @@
         <v>7.205</v>
       </c>
       <c r="M99">
-        <v>27.3785022</v>
+        <v>27.6607548</v>
       </c>
       <c r="N99">
-        <v>-20.17350219999999</v>
+        <v>-20.45575479999999</v>
       </c>
       <c r="O99">
-        <v>-5.043375549999999</v>
+        <v>-5.113938699999999</v>
       </c>
       <c r="P99">
-        <v>-15.13012665</v>
+        <v>-15.3418161</v>
       </c>
       <c r="Q99">
-        <v>-11.71012665</v>
+        <v>-11.9218161</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.911051352126619</v>
+        <v>2.843677028189928</v>
       </c>
       <c r="T99">
-        <v>18.03840615383538</v>
+        <v>27.05760923075307</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06579066987820832</v>
+        <v>0.06511933651210415</v>
       </c>
       <c r="W99">
-        <v>0.2202865600427185</v>
+        <v>0.2204448604504459</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2631626795128333</v>
+        <v>0.2604773460484167</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2729095038052355</v>
+        <v>0.2748095038052356</v>
       </c>
       <c r="C100">
-        <v>-70.10947869921959</v>
+        <v>-71.53460630791444</v>
       </c>
       <c r="D100">
-        <v>27.49652130078039</v>
+        <v>27.26839369208554</v>
       </c>
       <c r="E100">
-        <v>94.70599999999999</v>
+        <v>95.90299999999999</v>
       </c>
       <c r="F100">
-        <v>117.306</v>
+        <v>118.503</v>
       </c>
       <c r="G100">
         <v>19.7</v>
@@ -9487,37 +9487,37 @@
         <v>7.205</v>
       </c>
       <c r="M100">
-        <v>27.6607548</v>
+        <v>27.9430074</v>
       </c>
       <c r="N100">
-        <v>-20.45575479999999</v>
+        <v>-20.7380074</v>
       </c>
       <c r="O100">
-        <v>-5.113938699999999</v>
+        <v>-5.18450185</v>
       </c>
       <c r="P100">
-        <v>-15.3418161</v>
+        <v>-15.55350555</v>
       </c>
       <c r="Q100">
-        <v>-11.9218161</v>
+        <v>-12.13350555</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.843677028189928</v>
+        <v>5.641554056379857</v>
       </c>
       <c r="T100">
-        <v>27.05760923075307</v>
+        <v>54.11521846150615</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06511933651210415</v>
+        <v>0.06446156543622431</v>
       </c>
       <c r="W100">
-        <v>0.2204448604504459</v>
+        <v>0.2205999628701383</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2604773460484167</v>
+        <v>0.2578462617448972</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2748095038052356</v>
-      </c>
-      <c r="C101">
-        <v>-71.53460630791444</v>
-      </c>
-      <c r="D101">
-        <v>27.26839369208554</v>
-      </c>
-      <c r="E101">
-        <v>95.90299999999999</v>
-      </c>
-      <c r="F101">
-        <v>118.503</v>
-      </c>
-      <c r="G101">
-        <v>19.7</v>
-      </c>
-      <c r="H101">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.625</v>
-      </c>
-      <c r="K101">
-        <v>3.42</v>
-      </c>
-      <c r="L101">
-        <v>7.205</v>
-      </c>
-      <c r="M101">
-        <v>27.9430074</v>
-      </c>
-      <c r="N101">
-        <v>-20.7380074</v>
-      </c>
-      <c r="O101">
-        <v>-5.18450185</v>
-      </c>
-      <c r="P101">
-        <v>-15.55350555</v>
-      </c>
-      <c r="Q101">
-        <v>-12.13350555</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.641554056379857</v>
-      </c>
-      <c r="T101">
-        <v>54.11521846150615</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06446156543622431</v>
-      </c>
-      <c r="W101">
-        <v>0.2205999628701383</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2578462617448972</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
